--- a/outputs/식이_최종반영_20260922/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/식이_최종반영_20260922/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="Rb6fb7e89d976468c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문구세트" sheetId="2" r:id="R3dd5a23eb6b04466"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="축정의" sheetId="3" r:id="R832931268cfb4023"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상병코드매핑" sheetId="4" r:id="Ra6392eec82e2455f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정값" sheetId="5" r:id="Rf42730ace44644e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="Ra44f37f3f0e7477e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문구세트" sheetId="2" r:id="R4a40714006e94b60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="축정의" sheetId="3" r:id="Raefe4e995e49497f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상병코드매핑" sheetId="4" r:id="Re9966f2975084fcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정값" sheetId="5" r:id="R95ab452cde014e90"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -497,7 +497,7 @@
     </x:row>
     <x:row r="2" ht="38" customHeight="1">
       <x:c r="A2" s="21" t="str">
-        <x:v>운영 문구 163개. 불필요한 보류 62개 삭제. 사용=기획 후보; 전문의 최종 승인과 개인 제한 확인 전 실서비스 비활성.</x:v>
+        <x:v>운영 문구 163개. 불필요한 보류 62개 삭제. 사용=기획 후보; 운영 문구는 질환별 금지·시간·상황 조건으로 판정.</x:v>
       </x:c>
       <x:c r="B2" s="20"/>
       <x:c r="C2" s="20"/>
@@ -523,7 +523,7 @@
         <x:v>문구세트</x:v>
       </x:c>
       <x:c r="B5" s="18" t="str">
-        <x:v>163개 운영 문구·문구 ID·전문의 승인 필드</x:v>
+        <x:v>163개 운영 문구·문구 ID·출처 ID</x:v>
       </x:c>
       <x:c r="C5" s="18" t="n">
         <x:f>COUNTA(문구세트!G2:G164)</x:f>
@@ -535,7 +535,7 @@
         <x:v>축정의</x:v>
       </x:c>
       <x:c r="B6" s="18" t="str">
-        <x:v>8축 · 회전 문항 · 답 3개</x:v>
+        <x:v>8축 · 회전 문항 · 답 3개 · 질문 ID</x:v>
       </x:c>
       <x:c r="C6" s="18" t="n">
         <x:f>COUNTA(축정의!B2:B100)</x:f>
@@ -563,7 +563,7 @@
       </x:c>
       <x:c r="C8" s="18" t="n">
         <x:f>COUNTA(설정값!B2:B100)</x:f>
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="38" customHeight="1">
@@ -573,7 +573,7 @@
     </x:row>
     <x:row r="10" ht="38" customHeight="1">
       <x:c r="A10" s="23" t="str">
-        <x:v>문구 상태와 출시 승인은 별개</x:v>
+        <x:v>문구 사용 상태로 운영 후보 판정</x:v>
       </x:c>
       <x:c r="B10" s="20"/>
       <x:c r="C10" s="20"/>
@@ -583,7 +583,7 @@
         <x:v>사용</x:v>
       </x:c>
       <x:c r="B11" s="18" t="str">
-        <x:v>기획 후보. 전문의 승인 후 개인 조건 필터를 통과해야 노출</x:v>
+        <x:v>기획 후보. 질환별 금지·시간·상황 조건을 통과한 문구만 노출</x:v>
       </x:c>
       <x:c r="C11" s="18" t="n">
         <x:f>COUNTIF(문구세트!C2:C164,"사용")</x:f>
@@ -704,7 +704,7 @@
         <x:v>구분</x:v>
       </x:c>
       <x:c r="B25" s="18" t="str">
-        <x:v>상황 풀도 모든 안전·시간·승인 필터를 통과해야 함</x:v>
+        <x:v>상황 풀도 모든 질환별 금지·시간·상황 필터를 통과해야 함</x:v>
       </x:c>
       <x:c r="C25" s="18" t="str">
         <x:v>축 × 단계 · 회복 풀 · 부담 줄이기 풀</x:v>
@@ -825,7 +825,7 @@
         <x:v>검수 판정</x:v>
       </x:c>
       <x:c r="B36" s="18" t="str">
-        <x:v>AI 근거대조 결과. 실제 전문의 서명·최종 승인을 의미하지 않음</x:v>
+        <x:v>AI 근거대조 결과. 임상적 적합성 검토를 완료했다는 의미가 아님</x:v>
       </x:c>
       <x:c r="C36" s="18" t="str">
         <x:v>승인 · 조건부 · 수정 · 확인 필요 · 보류</x:v>
@@ -970,13 +970,9 @@
       <x:c r="C50" s="20"/>
     </x:row>
     <x:row r="51" ht="38" customHeight="1">
-      <x:c r="A51" s="20" t="str">
-        <x:v>출시 승인</x:v>
-      </x:c>
-      <x:c r="B51" s="20" t="str">
-        <x:v>설정값의 전문의 출시 승인 FALSE. 승인 필드는 미입력.</x:v>
-      </x:c>
-      <x:c r="C51" s="20"/>
+      <x:c r="A51"/>
+      <x:c r="B51"/>
+      <x:c r="C51"/>
     </x:row>
     <x:row r="52" ht="38" customHeight="1">
       <x:c r="A52" s="20" t="str">
@@ -1075,17 +1071,11 @@
         <x:v>문구 버전</x:v>
       </x:c>
       <x:c r="S1" s="20" t="str">
-        <x:v>전문의 승인 상태</x:v>
-      </x:c>
-      <x:c r="T1" s="20" t="str">
-        <x:v>승인자</x:v>
-      </x:c>
-      <x:c r="U1" s="20" t="str">
-        <x:v>승인일</x:v>
-      </x:c>
-      <x:c r="V1" s="20" t="str">
         <x:v>출처 ID</x:v>
       </x:c>
+      <x:c r="T1"/>
+      <x:c r="U1"/>
+      <x:c r="V1"/>
     </x:row>
     <x:row r="2" ht="84" customHeight="1">
       <x:c r="A2" s="18" t="n">
@@ -1142,13 +1132,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S2" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T2" s="20"/>
-      <x:c r="U2" s="20"/>
-      <x:c r="V2" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T2"/>
+      <x:c r="U2"/>
+      <x:c r="V2"/>
     </x:row>
     <x:row r="3" ht="84" customHeight="1">
       <x:c r="A3" s="18" t="n">
@@ -1205,13 +1193,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S3" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T3" s="20"/>
-      <x:c r="U3" s="20"/>
-      <x:c r="V3" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T3"/>
+      <x:c r="U3"/>
+      <x:c r="V3"/>
     </x:row>
     <x:row r="4" ht="84" customHeight="1">
       <x:c r="A4" s="18" t="n">
@@ -1266,13 +1252,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S4" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T4" s="20"/>
-      <x:c r="U4" s="20"/>
-      <x:c r="V4" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T4"/>
+      <x:c r="U4"/>
+      <x:c r="V4"/>
     </x:row>
     <x:row r="5" ht="84" customHeight="1">
       <x:c r="A5" s="18" t="n">
@@ -1327,13 +1311,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S5" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T5" s="20"/>
-      <x:c r="U5" s="20"/>
-      <x:c r="V5" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T5"/>
+      <x:c r="U5"/>
+      <x:c r="V5"/>
     </x:row>
     <x:row r="6" ht="84" customHeight="1">
       <x:c r="A6" s="18" t="n">
@@ -1388,13 +1370,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S6" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T6" s="20"/>
-      <x:c r="U6" s="20"/>
-      <x:c r="V6" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T6"/>
+      <x:c r="U6"/>
+      <x:c r="V6"/>
     </x:row>
     <x:row r="7" ht="84" customHeight="1">
       <x:c r="A7" s="18" t="n">
@@ -1449,13 +1429,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S7" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T7" s="20"/>
-      <x:c r="U7" s="20"/>
-      <x:c r="V7" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T7"/>
+      <x:c r="U7"/>
+      <x:c r="V7"/>
     </x:row>
     <x:row r="8" ht="84" customHeight="1">
       <x:c r="A8" s="18" t="n">
@@ -1512,13 +1490,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S8" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T8" s="20"/>
-      <x:c r="U8" s="20"/>
-      <x:c r="V8" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T8"/>
+      <x:c r="U8"/>
+      <x:c r="V8"/>
     </x:row>
     <x:row r="9" ht="84" customHeight="1">
       <x:c r="A9" s="18" t="n">
@@ -1573,13 +1549,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S9" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T9" s="20"/>
-      <x:c r="U9" s="20"/>
-      <x:c r="V9" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T9"/>
+      <x:c r="U9"/>
+      <x:c r="V9"/>
     </x:row>
     <x:row r="10" ht="84" customHeight="1">
       <x:c r="A10" s="18" t="n">
@@ -1634,13 +1608,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S10" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T10" s="20"/>
-      <x:c r="U10" s="20"/>
-      <x:c r="V10" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T10"/>
+      <x:c r="U10"/>
+      <x:c r="V10"/>
     </x:row>
     <x:row r="11" ht="84" customHeight="1">
       <x:c r="A11" s="18" t="n">
@@ -1695,13 +1667,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S11" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T11" s="20"/>
-      <x:c r="U11" s="20"/>
-      <x:c r="V11" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T11"/>
+      <x:c r="U11"/>
+      <x:c r="V11"/>
     </x:row>
     <x:row r="12" ht="84" customHeight="1">
       <x:c r="A12" s="18" t="n">
@@ -1758,13 +1728,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S12" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T12" s="20"/>
-      <x:c r="U12" s="20"/>
-      <x:c r="V12" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T12"/>
+      <x:c r="U12"/>
+      <x:c r="V12"/>
     </x:row>
     <x:row r="13" ht="84" customHeight="1">
       <x:c r="A13" s="18" t="n">
@@ -1819,13 +1787,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S13" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T13" s="20"/>
-      <x:c r="U13" s="20"/>
-      <x:c r="V13" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T13"/>
+      <x:c r="U13"/>
+      <x:c r="V13"/>
     </x:row>
     <x:row r="14" ht="84" customHeight="1">
       <x:c r="A14" s="18" t="n">
@@ -1880,13 +1846,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S14" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T14" s="20"/>
-      <x:c r="U14" s="20"/>
-      <x:c r="V14" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T14"/>
+      <x:c r="U14"/>
+      <x:c r="V14"/>
     </x:row>
     <x:row r="15" ht="84" customHeight="1">
       <x:c r="A15" s="18" t="n">
@@ -1941,13 +1905,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S15" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T15" s="20"/>
-      <x:c r="U15" s="20"/>
-      <x:c r="V15" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T15"/>
+      <x:c r="U15"/>
+      <x:c r="V15"/>
     </x:row>
     <x:row r="16" ht="84" customHeight="1">
       <x:c r="A16" s="18" t="n">
@@ -2002,13 +1964,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S16" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T16" s="20"/>
-      <x:c r="U16" s="20"/>
-      <x:c r="V16" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T16"/>
+      <x:c r="U16"/>
+      <x:c r="V16"/>
     </x:row>
     <x:row r="17" ht="84" customHeight="1">
       <x:c r="A17" s="18" t="n">
@@ -2063,13 +2023,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S17" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T17" s="20"/>
-      <x:c r="U17" s="20"/>
-      <x:c r="V17" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T17"/>
+      <x:c r="U17"/>
+      <x:c r="V17"/>
     </x:row>
     <x:row r="18" ht="84" customHeight="1">
       <x:c r="A18" s="18" t="n">
@@ -2124,13 +2082,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S18" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T18" s="20"/>
-      <x:c r="U18" s="20"/>
-      <x:c r="V18" s="20" t="str">
         <x:v>WHO-DIET / NICE-ED</x:v>
       </x:c>
+      <x:c r="T18"/>
+      <x:c r="U18"/>
+      <x:c r="V18"/>
     </x:row>
     <x:row r="19" ht="84" customHeight="1">
       <x:c r="A19" s="18" t="n">
@@ -2185,13 +2141,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S19" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T19" s="20"/>
-      <x:c r="U19" s="20"/>
-      <x:c r="V19" s="20" t="str">
         <x:v>WHO-DIET / NICE-ED</x:v>
       </x:c>
+      <x:c r="T19"/>
+      <x:c r="U19"/>
+      <x:c r="V19"/>
     </x:row>
     <x:row r="20" ht="84" customHeight="1">
       <x:c r="A20" s="18" t="n">
@@ -2246,13 +2200,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S20" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T20" s="20"/>
-      <x:c r="U20" s="20"/>
-      <x:c r="V20" s="20" t="str">
         <x:v>WHO-DIET / NICE-ED</x:v>
       </x:c>
+      <x:c r="T20"/>
+      <x:c r="U20"/>
+      <x:c r="V20"/>
     </x:row>
     <x:row r="21" ht="84" customHeight="1">
       <x:c r="A21" s="18" t="n">
@@ -2307,13 +2259,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S21" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T21" s="20"/>
-      <x:c r="U21" s="20"/>
-      <x:c r="V21" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T21"/>
+      <x:c r="U21"/>
+      <x:c r="V21"/>
     </x:row>
     <x:row r="22" ht="84" customHeight="1">
       <x:c r="A22" s="18" t="n">
@@ -2368,13 +2318,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S22" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T22" s="20"/>
-      <x:c r="U22" s="20"/>
-      <x:c r="V22" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T22"/>
+      <x:c r="U22"/>
+      <x:c r="V22"/>
     </x:row>
     <x:row r="23" ht="84" customHeight="1">
       <x:c r="A23" s="18" t="n">
@@ -2429,13 +2377,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S23" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T23" s="20"/>
-      <x:c r="U23" s="20"/>
-      <x:c r="V23" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T23"/>
+      <x:c r="U23"/>
+      <x:c r="V23"/>
     </x:row>
     <x:row r="24" ht="84" customHeight="1">
       <x:c r="A24" s="18" t="n">
@@ -2490,13 +2436,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S24" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T24" s="20"/>
-      <x:c r="U24" s="20"/>
-      <x:c r="V24" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T24"/>
+      <x:c r="U24"/>
+      <x:c r="V24"/>
     </x:row>
     <x:row r="25" ht="84" customHeight="1">
       <x:c r="A25" s="18" t="n">
@@ -2551,13 +2495,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S25" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T25" s="20"/>
-      <x:c r="U25" s="20"/>
-      <x:c r="V25" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T25"/>
+      <x:c r="U25"/>
+      <x:c r="V25"/>
     </x:row>
     <x:row r="26" ht="84" customHeight="1">
       <x:c r="A26" s="18" t="n">
@@ -2612,13 +2554,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S26" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T26" s="20"/>
-      <x:c r="U26" s="20"/>
-      <x:c r="V26" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T26"/>
+      <x:c r="U26"/>
+      <x:c r="V26"/>
     </x:row>
     <x:row r="27" ht="84" customHeight="1">
       <x:c r="A27" s="18" t="n">
@@ -2675,13 +2615,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S27" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T27" s="20"/>
-      <x:c r="U27" s="20"/>
-      <x:c r="V27" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T27"/>
+      <x:c r="U27"/>
+      <x:c r="V27"/>
     </x:row>
     <x:row r="28" ht="84" customHeight="1">
       <x:c r="A28" s="18" t="n">
@@ -2736,13 +2674,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S28" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T28" s="20"/>
-      <x:c r="U28" s="20"/>
-      <x:c r="V28" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T28"/>
+      <x:c r="U28"/>
+      <x:c r="V28"/>
     </x:row>
     <x:row r="29" ht="84" customHeight="1">
       <x:c r="A29" s="18" t="n">
@@ -2799,13 +2735,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S29" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T29" s="20"/>
-      <x:c r="U29" s="20"/>
-      <x:c r="V29" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T29"/>
+      <x:c r="U29"/>
+      <x:c r="V29"/>
     </x:row>
     <x:row r="30" ht="84" customHeight="1">
       <x:c r="A30" s="18" t="n">
@@ -2860,13 +2794,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S30" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T30" s="20"/>
-      <x:c r="U30" s="20"/>
-      <x:c r="V30" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T30"/>
+      <x:c r="U30"/>
+      <x:c r="V30"/>
     </x:row>
     <x:row r="31" ht="84" customHeight="1">
       <x:c r="A31" s="18" t="n">
@@ -2923,13 +2855,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S31" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T31" s="20"/>
-      <x:c r="U31" s="20"/>
-      <x:c r="V31" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T31"/>
+      <x:c r="U31"/>
+      <x:c r="V31"/>
     </x:row>
     <x:row r="32" ht="84" customHeight="1">
       <x:c r="A32" s="18" t="n">
@@ -2986,13 +2916,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S32" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T32" s="20"/>
-      <x:c r="U32" s="20"/>
-      <x:c r="V32" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T32"/>
+      <x:c r="U32"/>
+      <x:c r="V32"/>
     </x:row>
     <x:row r="33" ht="84" customHeight="1">
       <x:c r="A33" s="18" t="n">
@@ -3049,13 +2977,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S33" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T33" s="20"/>
-      <x:c r="U33" s="20"/>
-      <x:c r="V33" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD / AHA-HF</x:v>
       </x:c>
+      <x:c r="T33"/>
+      <x:c r="U33"/>
+      <x:c r="V33"/>
     </x:row>
     <x:row r="34" ht="84" customHeight="1">
       <x:c r="A34" s="18" t="n">
@@ -3112,13 +3038,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S34" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T34" s="20"/>
-      <x:c r="U34" s="20"/>
-      <x:c r="V34" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T34"/>
+      <x:c r="U34"/>
+      <x:c r="V34"/>
     </x:row>
     <x:row r="35" ht="84" customHeight="1">
       <x:c r="A35" s="18" t="n">
@@ -3175,13 +3099,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S35" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T35" s="20"/>
-      <x:c r="U35" s="20"/>
-      <x:c r="V35" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T35"/>
+      <x:c r="U35"/>
+      <x:c r="V35"/>
     </x:row>
     <x:row r="36" ht="84" customHeight="1">
       <x:c r="A36" s="18" t="n">
@@ -3238,13 +3160,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S36" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T36" s="20"/>
-      <x:c r="U36" s="20"/>
-      <x:c r="V36" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T36"/>
+      <x:c r="U36"/>
+      <x:c r="V36"/>
     </x:row>
     <x:row r="37" ht="84" customHeight="1">
       <x:c r="A37" s="18" t="n">
@@ -3301,13 +3221,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S37" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T37" s="20"/>
-      <x:c r="U37" s="20"/>
-      <x:c r="V37" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T37"/>
+      <x:c r="U37"/>
+      <x:c r="V37"/>
     </x:row>
     <x:row r="38" ht="84" customHeight="1">
       <x:c r="A38" s="18" t="n">
@@ -3355,7 +3273,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P38" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q38" s="20" t="str">
         <x:v>DIET-P-0045</x:v>
@@ -3364,13 +3282,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S38" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T38" s="20"/>
-      <x:c r="U38" s="20"/>
-      <x:c r="V38" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T38"/>
+      <x:c r="U38"/>
+      <x:c r="V38"/>
     </x:row>
     <x:row r="39" ht="84" customHeight="1">
       <x:c r="A39" s="18" t="n">
@@ -3427,13 +3343,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S39" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T39" s="20"/>
-      <x:c r="U39" s="20"/>
-      <x:c r="V39" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T39"/>
+      <x:c r="U39"/>
+      <x:c r="V39"/>
     </x:row>
     <x:row r="40" ht="84" customHeight="1">
       <x:c r="A40" s="18" t="n">
@@ -3490,13 +3404,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S40" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T40" s="20"/>
-      <x:c r="U40" s="20"/>
-      <x:c r="V40" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T40"/>
+      <x:c r="U40"/>
+      <x:c r="V40"/>
     </x:row>
     <x:row r="41" ht="84" customHeight="1">
       <x:c r="A41" s="18" t="n">
@@ -3544,7 +3456,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P41" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q41" s="20" t="str">
         <x:v>DIET-P-0048</x:v>
@@ -3553,13 +3465,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S41" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T41" s="20"/>
-      <x:c r="U41" s="20"/>
-      <x:c r="V41" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T41"/>
+      <x:c r="U41"/>
+      <x:c r="V41"/>
     </x:row>
     <x:row r="42" ht="84" customHeight="1">
       <x:c r="A42" s="18" t="n">
@@ -3616,13 +3526,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S42" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T42" s="20"/>
-      <x:c r="U42" s="20"/>
-      <x:c r="V42" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T42"/>
+      <x:c r="U42"/>
+      <x:c r="V42"/>
     </x:row>
     <x:row r="43" ht="84" customHeight="1">
       <x:c r="A43" s="18" t="n">
@@ -3679,13 +3587,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S43" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T43" s="20"/>
-      <x:c r="U43" s="20"/>
-      <x:c r="V43" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T43"/>
+      <x:c r="U43"/>
+      <x:c r="V43"/>
     </x:row>
     <x:row r="44" ht="84" customHeight="1">
       <x:c r="A44" s="18" t="n">
@@ -3742,13 +3648,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S44" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T44" s="20"/>
-      <x:c r="U44" s="20"/>
-      <x:c r="V44" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T44"/>
+      <x:c r="U44"/>
+      <x:c r="V44"/>
     </x:row>
     <x:row r="45" ht="84" customHeight="1">
       <x:c r="A45" s="18" t="n">
@@ -3805,13 +3709,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S45" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T45" s="20"/>
-      <x:c r="U45" s="20"/>
-      <x:c r="V45" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T45"/>
+      <x:c r="U45"/>
+      <x:c r="V45"/>
     </x:row>
     <x:row r="46" ht="84" customHeight="1">
       <x:c r="A46" s="18" t="n">
@@ -3868,13 +3770,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S46" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T46" s="20"/>
-      <x:c r="U46" s="20"/>
-      <x:c r="V46" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T46"/>
+      <x:c r="U46"/>
+      <x:c r="V46"/>
     </x:row>
     <x:row r="47" ht="84" customHeight="1">
       <x:c r="A47" s="18" t="n">
@@ -3931,13 +3831,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S47" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T47" s="20"/>
-      <x:c r="U47" s="20"/>
-      <x:c r="V47" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T47"/>
+      <x:c r="U47"/>
+      <x:c r="V47"/>
     </x:row>
     <x:row r="48" ht="84" customHeight="1">
       <x:c r="A48" s="18" t="n">
@@ -3994,13 +3892,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S48" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T48" s="20"/>
-      <x:c r="U48" s="20"/>
-      <x:c r="V48" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T48"/>
+      <x:c r="U48"/>
+      <x:c r="V48"/>
     </x:row>
     <x:row r="49" ht="84" customHeight="1">
       <x:c r="A49" s="18" t="n">
@@ -4057,13 +3953,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S49" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T49" s="20"/>
-      <x:c r="U49" s="20"/>
-      <x:c r="V49" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T49"/>
+      <x:c r="U49"/>
+      <x:c r="V49"/>
     </x:row>
     <x:row r="50" ht="84" customHeight="1">
       <x:c r="A50" s="18" t="n">
@@ -4111,7 +4005,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P50" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q50" s="20" t="str">
         <x:v>DIET-P-0058</x:v>
@@ -4120,13 +4014,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S50" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T50" s="20"/>
-      <x:c r="U50" s="20"/>
-      <x:c r="V50" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T50"/>
+      <x:c r="U50"/>
+      <x:c r="V50"/>
     </x:row>
     <x:row r="51" ht="84" customHeight="1">
       <x:c r="A51" s="18" t="n">
@@ -4183,13 +4075,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S51" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T51" s="20"/>
-      <x:c r="U51" s="20"/>
-      <x:c r="V51" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T51"/>
+      <x:c r="U51"/>
+      <x:c r="V51"/>
     </x:row>
     <x:row r="52" ht="84" customHeight="1">
       <x:c r="A52" s="18" t="n">
@@ -4246,13 +4136,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S52" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T52" s="20"/>
-      <x:c r="U52" s="20"/>
-      <x:c r="V52" s="20" t="str">
         <x:v>WHO-DIET / NICE-ED</x:v>
       </x:c>
+      <x:c r="T52"/>
+      <x:c r="U52"/>
+      <x:c r="V52"/>
     </x:row>
     <x:row r="53" ht="84" customHeight="1">
       <x:c r="A53" s="18" t="n">
@@ -4309,13 +4197,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S53" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T53" s="20"/>
-      <x:c r="U53" s="20"/>
-      <x:c r="V53" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T53"/>
+      <x:c r="U53"/>
+      <x:c r="V53"/>
     </x:row>
     <x:row r="54" ht="84" customHeight="1">
       <x:c r="A54" s="18" t="n">
@@ -4363,7 +4249,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P54" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q54" s="20" t="str">
         <x:v>DIET-P-0071</x:v>
@@ -4372,13 +4258,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S54" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T54" s="20"/>
-      <x:c r="U54" s="20"/>
-      <x:c r="V54" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD / AHA-HF</x:v>
       </x:c>
+      <x:c r="T54"/>
+      <x:c r="U54"/>
+      <x:c r="V54"/>
     </x:row>
     <x:row r="55" ht="84" customHeight="1">
       <x:c r="A55" s="18" t="n">
@@ -4426,7 +4310,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P55" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q55" s="20" t="str">
         <x:v>DIET-P-0072</x:v>
@@ -4435,13 +4319,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S55" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T55" s="20"/>
-      <x:c r="U55" s="20"/>
-      <x:c r="V55" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T55"/>
+      <x:c r="U55"/>
+      <x:c r="V55"/>
     </x:row>
     <x:row r="56" ht="84" customHeight="1">
       <x:c r="A56" s="18" t="n">
@@ -4498,13 +4380,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S56" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T56" s="20"/>
-      <x:c r="U56" s="20"/>
-      <x:c r="V56" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T56"/>
+      <x:c r="U56"/>
+      <x:c r="V56"/>
     </x:row>
     <x:row r="57" ht="84" customHeight="1">
       <x:c r="A57" s="18" t="n">
@@ -4561,13 +4441,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S57" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T57" s="20"/>
-      <x:c r="U57" s="20"/>
-      <x:c r="V57" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T57"/>
+      <x:c r="U57"/>
+      <x:c r="V57"/>
     </x:row>
     <x:row r="58" ht="84" customHeight="1">
       <x:c r="A58" s="18" t="n">
@@ -4624,13 +4502,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S58" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T58" s="20"/>
-      <x:c r="U58" s="20"/>
-      <x:c r="V58" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T58"/>
+      <x:c r="U58"/>
+      <x:c r="V58"/>
     </x:row>
     <x:row r="59" ht="84" customHeight="1">
       <x:c r="A59" s="18" t="n">
@@ -4687,13 +4563,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S59" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T59" s="20"/>
-      <x:c r="U59" s="20"/>
-      <x:c r="V59" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T59"/>
+      <x:c r="U59"/>
+      <x:c r="V59"/>
     </x:row>
     <x:row r="60" ht="84" customHeight="1">
       <x:c r="A60" s="18" t="n">
@@ -4750,13 +4624,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S60" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T60" s="20"/>
-      <x:c r="U60" s="20"/>
-      <x:c r="V60" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T60"/>
+      <x:c r="U60"/>
+      <x:c r="V60"/>
     </x:row>
     <x:row r="61" ht="84" customHeight="1">
       <x:c r="A61" s="18" t="n">
@@ -4813,13 +4685,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S61" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T61" s="20"/>
-      <x:c r="U61" s="20"/>
-      <x:c r="V61" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T61"/>
+      <x:c r="U61"/>
+      <x:c r="V61"/>
     </x:row>
     <x:row r="62" ht="84" customHeight="1">
       <x:c r="A62" s="18" t="n">
@@ -4876,13 +4746,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S62" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T62" s="20"/>
-      <x:c r="U62" s="20"/>
-      <x:c r="V62" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T62"/>
+      <x:c r="U62"/>
+      <x:c r="V62"/>
     </x:row>
     <x:row r="63" ht="84" customHeight="1">
       <x:c r="A63" s="18" t="n">
@@ -4939,13 +4807,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S63" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T63" s="20"/>
-      <x:c r="U63" s="20"/>
-      <x:c r="V63" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD / AHA-HF</x:v>
       </x:c>
+      <x:c r="T63"/>
+      <x:c r="U63"/>
+      <x:c r="V63"/>
     </x:row>
     <x:row r="64" ht="84" customHeight="1">
       <x:c r="A64" s="18" t="n">
@@ -5002,13 +4868,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S64" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T64" s="20"/>
-      <x:c r="U64" s="20"/>
-      <x:c r="V64" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T64"/>
+      <x:c r="U64"/>
+      <x:c r="V64"/>
     </x:row>
     <x:row r="65" ht="84" customHeight="1">
       <x:c r="A65" s="18" t="n">
@@ -5065,13 +4929,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S65" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T65" s="20"/>
-      <x:c r="U65" s="20"/>
-      <x:c r="V65" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T65"/>
+      <x:c r="U65"/>
+      <x:c r="V65"/>
     </x:row>
     <x:row r="66" ht="84" customHeight="1">
       <x:c r="A66" s="18" t="n">
@@ -5128,13 +4990,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S66" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T66" s="20"/>
-      <x:c r="U66" s="20"/>
-      <x:c r="V66" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T66"/>
+      <x:c r="U66"/>
+      <x:c r="V66"/>
     </x:row>
     <x:row r="67" ht="84" customHeight="1">
       <x:c r="A67" s="18" t="n">
@@ -5182,7 +5042,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P67" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q67" s="20" t="str">
         <x:v>DIET-P-0088</x:v>
@@ -5191,13 +5051,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S67" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T67" s="20"/>
-      <x:c r="U67" s="20"/>
-      <x:c r="V67" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T67"/>
+      <x:c r="U67"/>
+      <x:c r="V67"/>
     </x:row>
     <x:row r="68" ht="84" customHeight="1">
       <x:c r="A68" s="18" t="n">
@@ -5254,13 +5112,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S68" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T68" s="20"/>
-      <x:c r="U68" s="20"/>
-      <x:c r="V68" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T68"/>
+      <x:c r="U68"/>
+      <x:c r="V68"/>
     </x:row>
     <x:row r="69" ht="84" customHeight="1">
       <x:c r="A69" s="18" t="n">
@@ -5317,13 +5173,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S69" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T69" s="20"/>
-      <x:c r="U69" s="20"/>
-      <x:c r="V69" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T69"/>
+      <x:c r="U69"/>
+      <x:c r="V69"/>
     </x:row>
     <x:row r="70" ht="84" customHeight="1">
       <x:c r="A70" s="18" t="n">
@@ -5380,13 +5234,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S70" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T70" s="20"/>
-      <x:c r="U70" s="20"/>
-      <x:c r="V70" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T70"/>
+      <x:c r="U70"/>
+      <x:c r="V70"/>
     </x:row>
     <x:row r="71" ht="84" customHeight="1">
       <x:c r="A71" s="18" t="n">
@@ -5443,13 +5295,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S71" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T71" s="20"/>
-      <x:c r="U71" s="20"/>
-      <x:c r="V71" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T71"/>
+      <x:c r="U71"/>
+      <x:c r="V71"/>
     </x:row>
     <x:row r="72" ht="84" customHeight="1">
       <x:c r="A72" s="18" t="n">
@@ -5506,13 +5356,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S72" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T72" s="20"/>
-      <x:c r="U72" s="20"/>
-      <x:c r="V72" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T72"/>
+      <x:c r="U72"/>
+      <x:c r="V72"/>
     </x:row>
     <x:row r="73" ht="84" customHeight="1">
       <x:c r="A73" s="18" t="n">
@@ -5569,13 +5417,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S73" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T73" s="20"/>
-      <x:c r="U73" s="20"/>
-      <x:c r="V73" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T73"/>
+      <x:c r="U73"/>
+      <x:c r="V73"/>
     </x:row>
     <x:row r="74" ht="84" customHeight="1">
       <x:c r="A74" s="18" t="n">
@@ -5632,13 +5478,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S74" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T74" s="20"/>
-      <x:c r="U74" s="20"/>
-      <x:c r="V74" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T74"/>
+      <x:c r="U74"/>
+      <x:c r="V74"/>
     </x:row>
     <x:row r="75" ht="84" customHeight="1">
       <x:c r="A75" s="18" t="n">
@@ -5695,13 +5539,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S75" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T75" s="20"/>
-      <x:c r="U75" s="20"/>
-      <x:c r="V75" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T75"/>
+      <x:c r="U75"/>
+      <x:c r="V75"/>
     </x:row>
     <x:row r="76" ht="84" customHeight="1">
       <x:c r="A76" s="18" t="n">
@@ -5758,13 +5600,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S76" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T76" s="20"/>
-      <x:c r="U76" s="20"/>
-      <x:c r="V76" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T76"/>
+      <x:c r="U76"/>
+      <x:c r="V76"/>
     </x:row>
     <x:row r="77" ht="84" customHeight="1">
       <x:c r="A77" s="18" t="n">
@@ -5821,13 +5661,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S77" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T77" s="20"/>
-      <x:c r="U77" s="20"/>
-      <x:c r="V77" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T77"/>
+      <x:c r="U77"/>
+      <x:c r="V77"/>
     </x:row>
     <x:row r="78" ht="84" customHeight="1">
       <x:c r="A78" s="18" t="n">
@@ -5884,13 +5722,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S78" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T78" s="20"/>
-      <x:c r="U78" s="20"/>
-      <x:c r="V78" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T78"/>
+      <x:c r="U78"/>
+      <x:c r="V78"/>
     </x:row>
     <x:row r="79" ht="84" customHeight="1">
       <x:c r="A79" s="18" t="n">
@@ -5938,7 +5774,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P79" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q79" s="20" t="str">
         <x:v>DIET-P-0102</x:v>
@@ -5947,13 +5783,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S79" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T79" s="20"/>
-      <x:c r="U79" s="20"/>
-      <x:c r="V79" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T79"/>
+      <x:c r="U79"/>
+      <x:c r="V79"/>
     </x:row>
     <x:row r="80" ht="84" customHeight="1">
       <x:c r="A80" s="18" t="n">
@@ -6001,7 +5835,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P80" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q80" s="20" t="str">
         <x:v>DIET-P-0103</x:v>
@@ -6010,13 +5844,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S80" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T80" s="20"/>
-      <x:c r="U80" s="20"/>
-      <x:c r="V80" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T80"/>
+      <x:c r="U80"/>
+      <x:c r="V80"/>
     </x:row>
     <x:row r="81" ht="84" customHeight="1">
       <x:c r="A81" s="18" t="n">
@@ -6073,13 +5905,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S81" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T81" s="20"/>
-      <x:c r="U81" s="20"/>
-      <x:c r="V81" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T81"/>
+      <x:c r="U81"/>
+      <x:c r="V81"/>
     </x:row>
     <x:row r="82" ht="84" customHeight="1">
       <x:c r="A82" s="18" t="n">
@@ -6136,13 +5966,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S82" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T82" s="20"/>
-      <x:c r="U82" s="20"/>
-      <x:c r="V82" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T82"/>
+      <x:c r="U82"/>
+      <x:c r="V82"/>
     </x:row>
     <x:row r="83" ht="84" customHeight="1">
       <x:c r="A83" s="18" t="n">
@@ -6199,13 +6027,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S83" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T83" s="20"/>
-      <x:c r="U83" s="20"/>
-      <x:c r="V83" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T83"/>
+      <x:c r="U83"/>
+      <x:c r="V83"/>
     </x:row>
     <x:row r="84" ht="84" customHeight="1">
       <x:c r="A84" s="18" t="n">
@@ -6262,13 +6088,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S84" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T84" s="20"/>
-      <x:c r="U84" s="20"/>
-      <x:c r="V84" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T84"/>
+      <x:c r="U84"/>
+      <x:c r="V84"/>
     </x:row>
     <x:row r="85" ht="84" customHeight="1">
       <x:c r="A85" s="18" t="n">
@@ -6325,13 +6149,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S85" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T85" s="20"/>
-      <x:c r="U85" s="20"/>
-      <x:c r="V85" s="20" t="str">
         <x:v>WHO-DIET / NICE-ED</x:v>
       </x:c>
+      <x:c r="T85"/>
+      <x:c r="U85"/>
+      <x:c r="V85"/>
     </x:row>
     <x:row r="86" ht="84" customHeight="1">
       <x:c r="A86" s="18" t="n">
@@ -6388,13 +6210,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S86" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T86" s="20"/>
-      <x:c r="U86" s="20"/>
-      <x:c r="V86" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO / NICE-ED</x:v>
       </x:c>
+      <x:c r="T86"/>
+      <x:c r="U86"/>
+      <x:c r="V86"/>
     </x:row>
     <x:row r="87" ht="84" customHeight="1">
       <x:c r="A87" s="18" t="n">
@@ -6451,13 +6271,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S87" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T87" s="20"/>
-      <x:c r="U87" s="20"/>
-      <x:c r="V87" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO / NICE-ED</x:v>
       </x:c>
+      <x:c r="T87"/>
+      <x:c r="U87"/>
+      <x:c r="V87"/>
     </x:row>
     <x:row r="88" ht="84" customHeight="1">
       <x:c r="A88" s="18" t="n">
@@ -6505,7 +6323,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P88" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q88" s="20" t="str">
         <x:v>DIET-P-0115</x:v>
@@ -6514,13 +6332,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S88" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T88" s="20"/>
-      <x:c r="U88" s="20"/>
-      <x:c r="V88" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO / NICE-ED</x:v>
       </x:c>
+      <x:c r="T88"/>
+      <x:c r="U88"/>
+      <x:c r="V88"/>
     </x:row>
     <x:row r="89" ht="84" customHeight="1">
       <x:c r="A89" s="18" t="n">
@@ -6568,7 +6384,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P89" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q89" s="20" t="str">
         <x:v>DIET-P-0116</x:v>
@@ -6577,13 +6393,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S89" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T89" s="20"/>
-      <x:c r="U89" s="20"/>
-      <x:c r="V89" s="20" t="str">
         <x:v>WHO-DIET / NICE-ED</x:v>
       </x:c>
+      <x:c r="T89"/>
+      <x:c r="U89"/>
+      <x:c r="V89"/>
     </x:row>
     <x:row r="90" ht="84" customHeight="1">
       <x:c r="A90" s="18" t="n">
@@ -6640,13 +6454,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S90" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T90" s="20"/>
-      <x:c r="U90" s="20"/>
-      <x:c r="V90" s="20" t="str">
         <x:v>WHO-DIET / NICE-ED</x:v>
       </x:c>
+      <x:c r="T90"/>
+      <x:c r="U90"/>
+      <x:c r="V90"/>
     </x:row>
     <x:row r="91" ht="84" customHeight="1">
       <x:c r="A91" s="18" t="n">
@@ -6703,13 +6515,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S91" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T91" s="20"/>
-      <x:c r="U91" s="20"/>
-      <x:c r="V91" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T91"/>
+      <x:c r="U91"/>
+      <x:c r="V91"/>
     </x:row>
     <x:row r="92" ht="84" customHeight="1">
       <x:c r="A92" s="18" t="n">
@@ -6766,13 +6576,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S92" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T92" s="20"/>
-      <x:c r="U92" s="20"/>
-      <x:c r="V92" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T92"/>
+      <x:c r="U92"/>
+      <x:c r="V92"/>
     </x:row>
     <x:row r="93" ht="84" customHeight="1">
       <x:c r="A93" s="18" t="n">
@@ -6829,13 +6637,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S93" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T93" s="20"/>
-      <x:c r="U93" s="20"/>
-      <x:c r="V93" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T93"/>
+      <x:c r="U93"/>
+      <x:c r="V93"/>
     </x:row>
     <x:row r="94" ht="84" customHeight="1">
       <x:c r="A94" s="18" t="n">
@@ -6883,7 +6689,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P94" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q94" s="20" t="str">
         <x:v>DIET-P-0122</x:v>
@@ -6892,13 +6698,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S94" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T94" s="20"/>
-      <x:c r="U94" s="20"/>
-      <x:c r="V94" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T94"/>
+      <x:c r="U94"/>
+      <x:c r="V94"/>
     </x:row>
     <x:row r="95" ht="84" customHeight="1">
       <x:c r="A95" s="18" t="n">
@@ -6955,13 +6759,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S95" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T95" s="20"/>
-      <x:c r="U95" s="20"/>
-      <x:c r="V95" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T95"/>
+      <x:c r="U95"/>
+      <x:c r="V95"/>
     </x:row>
     <x:row r="96" ht="84" customHeight="1">
       <x:c r="A96" s="18" t="n">
@@ -7018,13 +6820,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S96" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T96" s="20"/>
-      <x:c r="U96" s="20"/>
-      <x:c r="V96" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T96"/>
+      <x:c r="U96"/>
+      <x:c r="V96"/>
     </x:row>
     <x:row r="97" ht="84" customHeight="1">
       <x:c r="A97" s="18" t="n">
@@ -7072,7 +6872,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P97" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q97" s="20" t="str">
         <x:v>DIET-P-0126</x:v>
@@ -7081,13 +6881,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S97" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T97" s="20"/>
-      <x:c r="U97" s="20"/>
-      <x:c r="V97" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T97"/>
+      <x:c r="U97"/>
+      <x:c r="V97"/>
     </x:row>
     <x:row r="98" ht="84" customHeight="1">
       <x:c r="A98" s="18" t="n">
@@ -7109,11 +6907,11 @@
         <x:v>입문</x:v>
       </x:c>
       <x:c r="G98" s="18" t="str">
-        <x:v>전날 밤에 아침거리 꺼내 두기</x:v>
+        <x:v>아침거리 미리 꺼내 두기</x:v>
       </x:c>
       <x:c r="H98" s="18" t="n">
         <x:f>LEN(G98)</x:f>
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="I98" s="18" t="str">
         <x:v>아침에 고민할 일이 없으면 덜 거르게 돼요.</x:v>
@@ -7135,7 +6933,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P98" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q98" s="20" t="str">
         <x:v>DIET-P-0131</x:v>
@@ -7144,13 +6942,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S98" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T98" s="20"/>
-      <x:c r="U98" s="20"/>
-      <x:c r="V98" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T98"/>
+      <x:c r="U98"/>
+      <x:c r="V98"/>
     </x:row>
     <x:row r="99" ht="84" customHeight="1">
       <x:c r="A99" s="18" t="n">
@@ -7198,7 +6994,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P99" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q99" s="20" t="str">
         <x:v>DIET-P-0132</x:v>
@@ -7207,13 +7003,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S99" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T99" s="20"/>
-      <x:c r="U99" s="20"/>
-      <x:c r="V99" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T99"/>
+      <x:c r="U99"/>
+      <x:c r="V99"/>
     </x:row>
     <x:row r="100" ht="84" customHeight="1">
       <x:c r="A100" s="18" t="n">
@@ -7261,7 +7055,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P100" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q100" s="20" t="str">
         <x:v>DIET-P-0133</x:v>
@@ -7270,13 +7064,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S100" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T100" s="20"/>
-      <x:c r="U100" s="20"/>
-      <x:c r="V100" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T100"/>
+      <x:c r="U100"/>
+      <x:c r="V100"/>
     </x:row>
     <x:row r="101" ht="84" customHeight="1">
       <x:c r="A101" s="18" t="n">
@@ -7324,7 +7116,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P101" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q101" s="20" t="str">
         <x:v>DIET-P-0134</x:v>
@@ -7333,13 +7125,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S101" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T101" s="20"/>
-      <x:c r="U101" s="20"/>
-      <x:c r="V101" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T101"/>
+      <x:c r="U101"/>
+      <x:c r="V101"/>
     </x:row>
     <x:row r="102" ht="84" customHeight="1">
       <x:c r="A102" s="18" t="n">
@@ -7396,13 +7186,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S102" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T102" s="20"/>
-      <x:c r="U102" s="20"/>
-      <x:c r="V102" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T102"/>
+      <x:c r="U102"/>
+      <x:c r="V102"/>
     </x:row>
     <x:row r="103" ht="84" customHeight="1">
       <x:c r="A103" s="18" t="n">
@@ -7459,13 +7247,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S103" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T103" s="20"/>
-      <x:c r="U103" s="20"/>
-      <x:c r="V103" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T103"/>
+      <x:c r="U103"/>
+      <x:c r="V103"/>
     </x:row>
     <x:row r="104" ht="84" customHeight="1">
       <x:c r="A104" s="18" t="n">
@@ -7513,7 +7299,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P104" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q104" s="20" t="str">
         <x:v>DIET-P-0137</x:v>
@@ -7522,13 +7308,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S104" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T104" s="20"/>
-      <x:c r="U104" s="20"/>
-      <x:c r="V104" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T104"/>
+      <x:c r="U104"/>
+      <x:c r="V104"/>
     </x:row>
     <x:row r="105" ht="84" customHeight="1">
       <x:c r="A105" s="18" t="n">
@@ -7576,7 +7360,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P105" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q105" s="20" t="str">
         <x:v>DIET-P-0138</x:v>
@@ -7585,13 +7369,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S105" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T105" s="20"/>
-      <x:c r="U105" s="20"/>
-      <x:c r="V105" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T105"/>
+      <x:c r="U105"/>
+      <x:c r="V105"/>
     </x:row>
     <x:row r="106" ht="84" customHeight="1">
       <x:c r="A106" s="18" t="n">
@@ -7648,13 +7430,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S106" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T106" s="20"/>
-      <x:c r="U106" s="20"/>
-      <x:c r="V106" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T106"/>
+      <x:c r="U106"/>
+      <x:c r="V106"/>
     </x:row>
     <x:row r="107" ht="84" customHeight="1">
       <x:c r="A107" s="18" t="n">
@@ -7711,13 +7491,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S107" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T107" s="20"/>
-      <x:c r="U107" s="20"/>
-      <x:c r="V107" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T107"/>
+      <x:c r="U107"/>
+      <x:c r="V107"/>
     </x:row>
     <x:row r="108" ht="84" customHeight="1">
       <x:c r="A108" s="18" t="n">
@@ -7765,7 +7543,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P108" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q108" s="20" t="str">
         <x:v>DIET-P-0141</x:v>
@@ -7774,13 +7552,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S108" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T108" s="20"/>
-      <x:c r="U108" s="20"/>
-      <x:c r="V108" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T108"/>
+      <x:c r="U108"/>
+      <x:c r="V108"/>
     </x:row>
     <x:row r="109" ht="84" customHeight="1">
       <x:c r="A109" s="18" t="n">
@@ -7828,7 +7604,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P109" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q109" s="20" t="str">
         <x:v>DIET-P-0143</x:v>
@@ -7837,13 +7613,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S109" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T109" s="20"/>
-      <x:c r="U109" s="20"/>
-      <x:c r="V109" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T109"/>
+      <x:c r="U109"/>
+      <x:c r="V109"/>
     </x:row>
     <x:row r="110" ht="84" customHeight="1">
       <x:c r="A110" s="18" t="n">
@@ -7891,7 +7665,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P110" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q110" s="20" t="str">
         <x:v>DIET-P-0144</x:v>
@@ -7900,13 +7674,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S110" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T110" s="20"/>
-      <x:c r="U110" s="20"/>
-      <x:c r="V110" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T110"/>
+      <x:c r="U110"/>
+      <x:c r="V110"/>
     </x:row>
     <x:row r="111" ht="84" customHeight="1">
       <x:c r="A111" s="18" t="n">
@@ -7963,13 +7735,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S111" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T111" s="20"/>
-      <x:c r="U111" s="20"/>
-      <x:c r="V111" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T111"/>
+      <x:c r="U111"/>
+      <x:c r="V111"/>
     </x:row>
     <x:row r="112" ht="84" customHeight="1">
       <x:c r="A112" s="18" t="n">
@@ -8026,13 +7796,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S112" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T112" s="20"/>
-      <x:c r="U112" s="20"/>
-      <x:c r="V112" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T112"/>
+      <x:c r="U112"/>
+      <x:c r="V112"/>
     </x:row>
     <x:row r="113" ht="84" customHeight="1">
       <x:c r="A113" s="18" t="n">
@@ -8080,7 +7848,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P113" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q113" s="20" t="str">
         <x:v>DIET-P-0147</x:v>
@@ -8089,13 +7857,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S113" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T113" s="20"/>
-      <x:c r="U113" s="20"/>
-      <x:c r="V113" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T113"/>
+      <x:c r="U113"/>
+      <x:c r="V113"/>
     </x:row>
     <x:row r="114" ht="84" customHeight="1">
       <x:c r="A114" s="18" t="n">
@@ -8152,13 +7918,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S114" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T114" s="20"/>
-      <x:c r="U114" s="20"/>
-      <x:c r="V114" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T114"/>
+      <x:c r="U114"/>
+      <x:c r="V114"/>
     </x:row>
     <x:row r="115" ht="84" customHeight="1">
       <x:c r="A115" s="18" t="n">
@@ -8206,7 +7970,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P115" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q115" s="20" t="str">
         <x:v>DIET-P-0149</x:v>
@@ -8215,13 +7979,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S115" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T115" s="20"/>
-      <x:c r="U115" s="20"/>
-      <x:c r="V115" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T115"/>
+      <x:c r="U115"/>
+      <x:c r="V115"/>
     </x:row>
     <x:row r="116" ht="84" customHeight="1">
       <x:c r="A116" s="18" t="n">
@@ -8278,13 +8040,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S116" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T116" s="20"/>
-      <x:c r="U116" s="20"/>
-      <x:c r="V116" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T116"/>
+      <x:c r="U116"/>
+      <x:c r="V116"/>
     </x:row>
     <x:row r="117" ht="84" customHeight="1">
       <x:c r="A117" s="18" t="n">
@@ -8332,7 +8092,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P117" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q117" s="20" t="str">
         <x:v>DIET-P-0151</x:v>
@@ -8341,13 +8101,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S117" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T117" s="20"/>
-      <x:c r="U117" s="20"/>
-      <x:c r="V117" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T117"/>
+      <x:c r="U117"/>
+      <x:c r="V117"/>
     </x:row>
     <x:row r="118" ht="84" customHeight="1">
       <x:c r="A118" s="18" t="n">
@@ -8404,13 +8162,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S118" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T118" s="20"/>
-      <x:c r="U118" s="20"/>
-      <x:c r="V118" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T118"/>
+      <x:c r="U118"/>
+      <x:c r="V118"/>
     </x:row>
     <x:row r="119" ht="84" customHeight="1">
       <x:c r="A119" s="18" t="n">
@@ -8467,13 +8223,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S119" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T119" s="20"/>
-      <x:c r="U119" s="20"/>
-      <x:c r="V119" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T119"/>
+      <x:c r="U119"/>
+      <x:c r="V119"/>
     </x:row>
     <x:row r="120" ht="84" customHeight="1">
       <x:c r="A120" s="18" t="n">
@@ -8530,13 +8284,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S120" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T120" s="20"/>
-      <x:c r="U120" s="20"/>
-      <x:c r="V120" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T120"/>
+      <x:c r="U120"/>
+      <x:c r="V120"/>
     </x:row>
     <x:row r="121" ht="84" customHeight="1">
       <x:c r="A121" s="18" t="n">
@@ -8593,13 +8345,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S121" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T121" s="20"/>
-      <x:c r="U121" s="20"/>
-      <x:c r="V121" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO / NICE-ED</x:v>
       </x:c>
+      <x:c r="T121"/>
+      <x:c r="U121"/>
+      <x:c r="V121"/>
     </x:row>
     <x:row r="122" ht="84" customHeight="1">
       <x:c r="A122" s="18" t="n">
@@ -8647,7 +8397,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P122" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q122" s="20" t="str">
         <x:v>DIET-P-0156</x:v>
@@ -8656,13 +8406,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S122" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T122" s="20"/>
-      <x:c r="U122" s="20"/>
-      <x:c r="V122" s="20" t="str">
         <x:v>WHO-DIET / NICE-ED</x:v>
       </x:c>
+      <x:c r="T122"/>
+      <x:c r="U122"/>
+      <x:c r="V122"/>
     </x:row>
     <x:row r="123" ht="84" customHeight="1">
       <x:c r="A123" s="18" t="n">
@@ -8719,13 +8467,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S123" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T123" s="20"/>
-      <x:c r="U123" s="20"/>
-      <x:c r="V123" s="20" t="str">
         <x:v>WHO-DIET / NICE-ED</x:v>
       </x:c>
+      <x:c r="T123"/>
+      <x:c r="U123"/>
+      <x:c r="V123"/>
     </x:row>
     <x:row r="124" ht="84" customHeight="1">
       <x:c r="A124" s="18" t="n">
@@ -8782,13 +8528,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S124" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T124" s="20"/>
-      <x:c r="U124" s="20"/>
-      <x:c r="V124" s="20" t="str">
         <x:v>WHO-DIET / NICE-ED</x:v>
       </x:c>
+      <x:c r="T124"/>
+      <x:c r="U124"/>
+      <x:c r="V124"/>
     </x:row>
     <x:row r="125" ht="84" customHeight="1">
       <x:c r="A125" s="18" t="n">
@@ -8836,7 +8580,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P125" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q125" s="20" t="str">
         <x:v>DIET-P-0161</x:v>
@@ -8845,13 +8589,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S125" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T125" s="20"/>
-      <x:c r="U125" s="20"/>
-      <x:c r="V125" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO / NICE-ED</x:v>
       </x:c>
+      <x:c r="T125"/>
+      <x:c r="U125"/>
+      <x:c r="V125"/>
     </x:row>
     <x:row r="126" ht="84" customHeight="1">
       <x:c r="A126" s="18" t="n">
@@ -8899,7 +8641,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P126" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q126" s="20" t="str">
         <x:v>DIET-P-0163</x:v>
@@ -8908,13 +8650,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S126" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T126" s="20"/>
-      <x:c r="U126" s="20"/>
-      <x:c r="V126" s="20" t="str">
         <x:v>WHO-DIET / NICE-ED</x:v>
       </x:c>
+      <x:c r="T126"/>
+      <x:c r="U126"/>
+      <x:c r="V126"/>
     </x:row>
     <x:row r="127" ht="84" customHeight="1">
       <x:c r="A127" s="18" t="n">
@@ -8962,7 +8702,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P127" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q127" s="20" t="str">
         <x:v>DIET-P-0165</x:v>
@@ -8971,13 +8711,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S127" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T127" s="20"/>
-      <x:c r="U127" s="20"/>
-      <x:c r="V127" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T127"/>
+      <x:c r="U127"/>
+      <x:c r="V127"/>
     </x:row>
     <x:row r="128" ht="84" customHeight="1">
       <x:c r="A128" s="18" t="n">
@@ -9025,7 +8763,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P128" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q128" s="20" t="str">
         <x:v>DIET-P-0166</x:v>
@@ -9034,13 +8772,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S128" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T128" s="20"/>
-      <x:c r="U128" s="20"/>
-      <x:c r="V128" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T128"/>
+      <x:c r="U128"/>
+      <x:c r="V128"/>
     </x:row>
     <x:row r="129" ht="84" customHeight="1">
       <x:c r="A129" s="18" t="n">
@@ -9088,7 +8824,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P129" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q129" s="20" t="str">
         <x:v>DIET-P-0167</x:v>
@@ -9097,13 +8833,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S129" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T129" s="20"/>
-      <x:c r="U129" s="20"/>
-      <x:c r="V129" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T129"/>
+      <x:c r="U129"/>
+      <x:c r="V129"/>
     </x:row>
     <x:row r="130" ht="84" customHeight="1">
       <x:c r="A130" s="18" t="n">
@@ -9160,13 +8894,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S130" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T130" s="20"/>
-      <x:c r="U130" s="20"/>
-      <x:c r="V130" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T130"/>
+      <x:c r="U130"/>
+      <x:c r="V130"/>
     </x:row>
     <x:row r="131" ht="84" customHeight="1">
       <x:c r="A131" s="18" t="n">
@@ -9223,13 +8955,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S131" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T131" s="20"/>
-      <x:c r="U131" s="20"/>
-      <x:c r="V131" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T131"/>
+      <x:c r="U131"/>
+      <x:c r="V131"/>
     </x:row>
     <x:row r="132" ht="84" customHeight="1">
       <x:c r="A132" s="18" t="n">
@@ -9277,7 +9007,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P132" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q132" s="20" t="str">
         <x:v>DIET-P-0170</x:v>
@@ -9286,13 +9016,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S132" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T132" s="20"/>
-      <x:c r="U132" s="20"/>
-      <x:c r="V132" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T132"/>
+      <x:c r="U132"/>
+      <x:c r="V132"/>
     </x:row>
     <x:row r="133" ht="84" customHeight="1">
       <x:c r="A133" s="18" t="n">
@@ -9349,13 +9077,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S133" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T133" s="20"/>
-      <x:c r="U133" s="20"/>
-      <x:c r="V133" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T133"/>
+      <x:c r="U133"/>
+      <x:c r="V133"/>
     </x:row>
     <x:row r="134" ht="84" customHeight="1">
       <x:c r="A134" s="18" t="n">
@@ -9412,13 +9138,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S134" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T134" s="20"/>
-      <x:c r="U134" s="20"/>
-      <x:c r="V134" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T134"/>
+      <x:c r="U134"/>
+      <x:c r="V134"/>
     </x:row>
     <x:row r="135" ht="84" customHeight="1">
       <x:c r="A135" s="18" t="n">
@@ -9475,13 +9199,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S135" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T135" s="20"/>
-      <x:c r="U135" s="20"/>
-      <x:c r="V135" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T135"/>
+      <x:c r="U135"/>
+      <x:c r="V135"/>
     </x:row>
     <x:row r="136" ht="84" customHeight="1">
       <x:c r="A136" s="18" t="n">
@@ -9538,13 +9260,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S136" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T136" s="20"/>
-      <x:c r="U136" s="20"/>
-      <x:c r="V136" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T136"/>
+      <x:c r="U136"/>
+      <x:c r="V136"/>
     </x:row>
     <x:row r="137" ht="84" customHeight="1">
       <x:c r="A137" s="18" t="n">
@@ -9601,13 +9321,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S137" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T137" s="20"/>
-      <x:c r="U137" s="20"/>
-      <x:c r="V137" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T137"/>
+      <x:c r="U137"/>
+      <x:c r="V137"/>
     </x:row>
     <x:row r="138" ht="84" customHeight="1">
       <x:c r="A138" s="18" t="n">
@@ -9664,13 +9382,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S138" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T138" s="20"/>
-      <x:c r="U138" s="20"/>
-      <x:c r="V138" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T138"/>
+      <x:c r="U138"/>
+      <x:c r="V138"/>
     </x:row>
     <x:row r="139" ht="84" customHeight="1">
       <x:c r="A139" s="18" t="n">
@@ -9727,13 +9443,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S139" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T139" s="20"/>
-      <x:c r="U139" s="20"/>
-      <x:c r="V139" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T139"/>
+      <x:c r="U139"/>
+      <x:c r="V139"/>
     </x:row>
     <x:row r="140" ht="84" customHeight="1">
       <x:c r="A140" s="18" t="n">
@@ -9790,13 +9504,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S140" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T140" s="20"/>
-      <x:c r="U140" s="20"/>
-      <x:c r="V140" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T140"/>
+      <x:c r="U140"/>
+      <x:c r="V140"/>
     </x:row>
     <x:row r="141" ht="84" customHeight="1">
       <x:c r="A141" s="18" t="n">
@@ -9844,7 +9556,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P141" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q141" s="20" t="str">
         <x:v>DIET-P-0198</x:v>
@@ -9853,13 +9565,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S141" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T141" s="20"/>
-      <x:c r="U141" s="20"/>
-      <x:c r="V141" s="20" t="str">
         <x:v>WHO-DIET / NICE-ED</x:v>
       </x:c>
+      <x:c r="T141"/>
+      <x:c r="U141"/>
+      <x:c r="V141"/>
     </x:row>
     <x:row r="142" ht="84" customHeight="1">
       <x:c r="A142" s="18" t="n">
@@ -9907,7 +9617,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P142" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q142" s="20" t="str">
         <x:v>DIET-P-0199</x:v>
@@ -9916,13 +9626,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S142" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T142" s="20"/>
-      <x:c r="U142" s="20"/>
-      <x:c r="V142" s="20" t="str">
         <x:v>WHO-DIET / NICE-ED</x:v>
       </x:c>
+      <x:c r="T142"/>
+      <x:c r="U142"/>
+      <x:c r="V142"/>
     </x:row>
     <x:row r="143" ht="84" customHeight="1">
       <x:c r="A143" s="18" t="n">
@@ -9979,13 +9687,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S143" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T143" s="20"/>
-      <x:c r="U143" s="20"/>
-      <x:c r="V143" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T143"/>
+      <x:c r="U143"/>
+      <x:c r="V143"/>
     </x:row>
     <x:row r="144" ht="84" customHeight="1">
       <x:c r="A144" s="18" t="n">
@@ -10042,13 +9748,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S144" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T144" s="20"/>
-      <x:c r="U144" s="20"/>
-      <x:c r="V144" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T144"/>
+      <x:c r="U144"/>
+      <x:c r="V144"/>
     </x:row>
     <x:row r="145" ht="84" customHeight="1">
       <x:c r="A145" s="18" t="n">
@@ -10096,7 +9800,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P145" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q145" s="20" t="str">
         <x:v>DIET-P-0202</x:v>
@@ -10105,13 +9809,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S145" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T145" s="20"/>
-      <x:c r="U145" s="20"/>
-      <x:c r="V145" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T145"/>
+      <x:c r="U145"/>
+      <x:c r="V145"/>
     </x:row>
     <x:row r="146" ht="84" customHeight="1">
       <x:c r="A146" s="18" t="n">
@@ -10168,13 +9870,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S146" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T146" s="20"/>
-      <x:c r="U146" s="20"/>
-      <x:c r="V146" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T146"/>
+      <x:c r="U146"/>
+      <x:c r="V146"/>
     </x:row>
     <x:row r="147" ht="84" customHeight="1">
       <x:c r="A147" s="18" t="n">
@@ -10222,7 +9922,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P147" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q147" s="20" t="str">
         <x:v>DIET-P-0205</x:v>
@@ -10231,13 +9931,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S147" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T147" s="20"/>
-      <x:c r="U147" s="20"/>
-      <x:c r="V147" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO / NICE-ED</x:v>
       </x:c>
+      <x:c r="T147"/>
+      <x:c r="U147"/>
+      <x:c r="V147"/>
     </x:row>
     <x:row r="148" ht="84" customHeight="1">
       <x:c r="A148" s="18" t="n">
@@ -10294,13 +9992,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S148" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T148" s="20"/>
-      <x:c r="U148" s="20"/>
-      <x:c r="V148" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T148"/>
+      <x:c r="U148"/>
+      <x:c r="V148"/>
     </x:row>
     <x:row r="149" ht="84" customHeight="1">
       <x:c r="A149" s="18" t="n">
@@ -10357,13 +10053,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S149" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T149" s="20"/>
-      <x:c r="U149" s="20"/>
-      <x:c r="V149" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T149"/>
+      <x:c r="U149"/>
+      <x:c r="V149"/>
     </x:row>
     <x:row r="150" ht="84" customHeight="1">
       <x:c r="A150" s="18" t="n">
@@ -10411,7 +10105,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P150" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q150" s="20" t="str">
         <x:v>DIET-P-0208</x:v>
@@ -10420,13 +10114,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S150" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T150" s="20"/>
-      <x:c r="U150" s="20"/>
-      <x:c r="V150" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T150"/>
+      <x:c r="U150"/>
+      <x:c r="V150"/>
     </x:row>
     <x:row r="151" ht="84" customHeight="1">
       <x:c r="A151" s="18" t="n">
@@ -10474,7 +10166,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P151" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q151" s="20" t="str">
         <x:v>DIET-P-0209</x:v>
@@ -10483,13 +10175,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S151" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T151" s="20"/>
-      <x:c r="U151" s="20"/>
-      <x:c r="V151" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T151"/>
+      <x:c r="U151"/>
+      <x:c r="V151"/>
     </x:row>
     <x:row r="152" ht="84" customHeight="1">
       <x:c r="A152" s="18" t="n">
@@ -10546,13 +10236,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S152" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T152" s="20"/>
-      <x:c r="U152" s="20"/>
-      <x:c r="V152" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T152"/>
+      <x:c r="U152"/>
+      <x:c r="V152"/>
     </x:row>
     <x:row r="153" ht="84" customHeight="1">
       <x:c r="A153" s="18" t="n">
@@ -10609,13 +10297,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S153" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T153" s="20"/>
-      <x:c r="U153" s="20"/>
-      <x:c r="V153" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T153"/>
+      <x:c r="U153"/>
+      <x:c r="V153"/>
     </x:row>
     <x:row r="154" ht="84" customHeight="1">
       <x:c r="A154" s="18" t="n">
@@ -10663,7 +10349,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P154" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q154" s="20" t="str">
         <x:v>DIET-P-0212</x:v>
@@ -10672,13 +10358,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S154" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T154" s="20"/>
-      <x:c r="U154" s="20"/>
-      <x:c r="V154" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-CKD</x:v>
       </x:c>
+      <x:c r="T154"/>
+      <x:c r="U154"/>
+      <x:c r="V154"/>
     </x:row>
     <x:row r="155" ht="84" customHeight="1">
       <x:c r="A155" s="18" t="n">
@@ -10735,13 +10419,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S155" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T155" s="20"/>
-      <x:c r="U155" s="20"/>
-      <x:c r="V155" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T155"/>
+      <x:c r="U155"/>
+      <x:c r="V155"/>
     </x:row>
     <x:row r="156" ht="84" customHeight="1">
       <x:c r="A156" s="18" t="n">
@@ -10798,13 +10480,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S156" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T156" s="20"/>
-      <x:c r="U156" s="20"/>
-      <x:c r="V156" s="20" t="str">
         <x:v>WHO-DIET / NICE-ED</x:v>
       </x:c>
+      <x:c r="T156"/>
+      <x:c r="U156"/>
+      <x:c r="V156"/>
     </x:row>
     <x:row r="157" ht="84" customHeight="1">
       <x:c r="A157" s="18" t="n">
@@ -10861,13 +10541,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S157" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T157" s="20"/>
-      <x:c r="U157" s="20"/>
-      <x:c r="V157" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T157"/>
+      <x:c r="U157"/>
+      <x:c r="V157"/>
     </x:row>
     <x:row r="158" ht="84" customHeight="1">
       <x:c r="A158" s="18" t="n">
@@ -10915,7 +10593,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P158" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q158" s="20" t="str">
         <x:v>DIET-P-0217</x:v>
@@ -10924,13 +10602,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S158" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T158" s="20"/>
-      <x:c r="U158" s="20"/>
-      <x:c r="V158" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T158"/>
+      <x:c r="U158"/>
+      <x:c r="V158"/>
     </x:row>
     <x:row r="159" ht="84" customHeight="1">
       <x:c r="A159" s="18" t="n">
@@ -10987,13 +10663,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S159" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T159" s="20"/>
-      <x:c r="U159" s="20"/>
-      <x:c r="V159" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T159"/>
+      <x:c r="U159"/>
+      <x:c r="V159"/>
     </x:row>
     <x:row r="160" ht="84" customHeight="1">
       <x:c r="A160" s="18" t="n">
@@ -11050,13 +10724,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S160" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T160" s="20"/>
-      <x:c r="U160" s="20"/>
-      <x:c r="V160" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T160"/>
+      <x:c r="U160"/>
+      <x:c r="V160"/>
     </x:row>
     <x:row r="161" ht="84" customHeight="1">
       <x:c r="A161" s="18" t="n">
@@ -11113,13 +10785,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S161" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T161" s="20"/>
-      <x:c r="U161" s="20"/>
-      <x:c r="V161" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T161"/>
+      <x:c r="U161"/>
+      <x:c r="V161"/>
     </x:row>
     <x:row r="162" ht="84" customHeight="1">
       <x:c r="A162" s="18" t="n">
@@ -11176,13 +10846,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S162" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T162" s="20"/>
-      <x:c r="U162" s="20"/>
-      <x:c r="V162" s="20" t="str">
         <x:v>WHO-DIET / NIDDK-HYPO</x:v>
       </x:c>
+      <x:c r="T162"/>
+      <x:c r="U162"/>
+      <x:c r="V162"/>
     </x:row>
     <x:row r="163" ht="84" customHeight="1">
       <x:c r="A163" s="18" t="n">
@@ -11239,13 +10907,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S163" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T163" s="20"/>
-      <x:c r="U163" s="20"/>
-      <x:c r="V163" s="20" t="str">
         <x:v>WHO-DIET</x:v>
       </x:c>
+      <x:c r="T163"/>
+      <x:c r="U163"/>
+      <x:c r="V163"/>
     </x:row>
     <x:row r="164" ht="84" customHeight="1">
       <x:c r="A164" s="18" t="n">
@@ -11293,7 +10959,7 @@
         <x:v>근거대조·조건 확인</x:v>
       </x:c>
       <x:c r="P164" s="18" t="str">
-        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·전문의 승인 미확정</x:v>
+        <x:v>효과 단정 없이 행동 설명으로 유지. 개인별 적합성·문구 적합성 검토 필요</x:v>
       </x:c>
       <x:c r="Q164" s="20" t="str">
         <x:v>DIET-P-0225</x:v>
@@ -11302,13 +10968,11 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="S164" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="T164" s="20"/>
-      <x:c r="U164" s="20"/>
-      <x:c r="V164" s="20" t="str">
         <x:v>WHO-DIET / AHA-HF</x:v>
       </x:c>
+      <x:c r="T164"/>
+      <x:c r="U164"/>
+      <x:c r="V164"/>
     </x:row>
     <x:row r="165" ht="84" customHeight="1">
       <x:c r="A165"/>
@@ -12983,10 +12647,10 @@
         <x:v>채소</x:v>
       </x:c>
       <x:c r="C3" s="18" t="str">
-        <x:v>채소 반찬 종류 수. 중량·먹는 순서 아님</x:v>
+        <x:v>실제로 먹은 채소 반찬 종류 수. 중량·먹는 순서 아님</x:v>
       </x:c>
       <x:c r="D3" s="18" t="str">
-        <x:v>{지난 끼니}에 채소 반찬이 있었나요?</x:v>
+        <x:v>{지난 끼니}에 채소 반찬을 몇 가지 드셨나요?</x:v>
       </x:c>
       <x:c r="E3" s="18" t="str">
         <x:v>두 가지 이상</x:v>
@@ -12995,7 +12659,7 @@
         <x:v>한 가지</x:v>
       </x:c>
       <x:c r="G3" s="18" t="str">
-        <x:v>없었어요</x:v>
+        <x:v>먹지 않았어요</x:v>
       </x:c>
       <x:c r="H3" s="18" t="str">
         <x:v>모든 끼니</x:v>
@@ -13039,19 +12703,19 @@
         <x:v>단 음료 · 단 간식</x:v>
       </x:c>
       <x:c r="C4" s="18" t="str">
-        <x:v>가당 음료·단 간식 섭취 여부. 총당량 아님</x:v>
+        <x:v>단 음료·단 간식 섭취 횟수. 양·총당량 아님</x:v>
       </x:c>
       <x:c r="D4" s="18" t="str">
-        <x:v>{지난 끼니} 전후 단 음료·간식을 드셨나요?</x:v>
+        <x:v>{지난 끼니} 전후에 단 음료나 단 간식을 몇 번 드셨나요?</x:v>
       </x:c>
       <x:c r="E4" s="18" t="str">
-        <x:v>안 먹었어요</x:v>
+        <x:v>없었어요</x:v>
       </x:c>
       <x:c r="F4" s="18" t="str">
-        <x:v>먹었어요</x:v>
+        <x:v>한 번</x:v>
       </x:c>
       <x:c r="G4" s="18" t="str">
-        <x:v>기억이 안 나요</x:v>
+        <x:v>두 번 이상</x:v>
       </x:c>
       <x:c r="H4" s="18" t="str">
         <x:v>모든 끼니</x:v>
@@ -13060,7 +12724,7 @@
         <x:v>혈당 · 체중 · 당뇨</x:v>
       </x:c>
       <x:c r="J4" s="18" t="str">
-        <x:v>저혈당 처치용 섭취는 불리한 응답으로 평가하지 않음. 해당 위험 시 축 집계/목표 제한</x:v>
+        <x:v>섭취 횟수만 관찰. 저혈당 처치용 섭취는 불리한 응답으로 평가하지 않음</x:v>
       </x:c>
       <x:c r="K4" s="20" t="str">
         <x:v>DIET-Q-02</x:v>
@@ -13072,18 +12736,20 @@
         <x:v>none</x:v>
       </x:c>
       <x:c r="N4" s="20" t="str">
-        <x:v>some</x:v>
+        <x:v>once</x:v>
       </x:c>
       <x:c r="O4" s="20" t="str">
-        <x:v>unknown</x:v>
+        <x:v>twice_or_more</x:v>
       </x:c>
       <x:c r="P4" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q4" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R4" s="20" t="n">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="R4" s="20"/>
     </x:row>
     <x:row r="5" ht="88" customHeight="1">
       <x:c r="A5" s="18" t="n">
@@ -13093,19 +12759,19 @@
         <x:v>짠맛 · 국물</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
-        <x:v>국물 섭취 정도. 전체 나트륨 아님</x:v>
+        <x:v>제공된 국물 중 먹은 대략 비율. 전체 나트륨 아님</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
-        <x:v>{지난 끼니} 국물은 어느 정도 드셨나요?</x:v>
+        <x:v>{지난 끼니}에 국물은 얼마나 드셨나요?</x:v>
       </x:c>
       <x:c r="E5" s="18" t="str">
         <x:v>안 먹었어요</x:v>
       </x:c>
       <x:c r="F5" s="18" t="str">
-        <x:v>일부 먹었어요</x:v>
+        <x:v>절반 이하 먹었어요</x:v>
       </x:c>
       <x:c r="G5" s="18" t="str">
-        <x:v>거의 다 먹었어요</x:v>
+        <x:v>절반보다 많이 먹었어요</x:v>
       </x:c>
       <x:c r="H5" s="18" t="str">
         <x:v>모든 끼니</x:v>
@@ -13126,10 +12792,10 @@
         <x:v>none</x:v>
       </x:c>
       <x:c r="N5" s="20" t="str">
-        <x:v>some</x:v>
+        <x:v>half_or_less</x:v>
       </x:c>
       <x:c r="O5" s="20" t="str">
-        <x:v>most</x:v>
+        <x:v>more_than_half</x:v>
       </x:c>
       <x:c r="P5" s="20" t="n">
         <x:v>1</x:v>
@@ -13149,28 +12815,28 @@
         <x:v>식사 시각</x:v>
       </x:c>
       <x:c r="C6" s="18" t="str">
-        <x:v>저녁 이후 추가 섭취 여부. 야식 위해성·수면 판정 아님</x:v>
+        <x:v>전날 저녁 식사 후~당일 04:00 전의 야식 자기보고 횟수. 오늘 아침 식사는 제외. 위해성·수면 영향 판정 아님</x:v>
       </x:c>
       <x:c r="D6" s="18" t="str">
-        <x:v>어제 저녁 식사 뒤에 더 드셨나요?</x:v>
+        <x:v>어젯밤 야식을 몇 번 드셨나요?</x:v>
       </x:c>
       <x:c r="E6" s="18" t="str">
         <x:v>안 먹었어요</x:v>
       </x:c>
       <x:c r="F6" s="18" t="str">
-        <x:v>먹었어요</x:v>
+        <x:v>한 번 먹었어요</x:v>
       </x:c>
       <x:c r="G6" s="18" t="str">
-        <x:v>기억이 안 나요</x:v>
+        <x:v>두 번 이상 먹었어요</x:v>
       </x:c>
       <x:c r="H6" s="18" t="str">
-        <x:v>어제 저녁만</x:v>
+        <x:v>04:00~10:00 진입에서만(전날 밤 회상)</x:v>
       </x:c>
       <x:c r="I6" s="18" t="str">
         <x:v>체중 · 비만 · 역류</x:v>
       </x:c>
       <x:c r="J6" s="18" t="str">
-        <x:v>사실 빈도만 저장. 필요한 간식·교대근무 구분 불가하므로 좋음/나쁨 등급 산출 중지</x:v>
+        <x:v>야식 여부·횟수만 저장. 필요한 간식과 교대근무 상황은 구분할 수 없어 좋음/나쁨 등급 산출 중지</x:v>
       </x:c>
       <x:c r="K6" s="20" t="str">
         <x:v>DIET-Q-04</x:v>
@@ -13182,10 +12848,10 @@
         <x:v>none</x:v>
       </x:c>
       <x:c r="N6" s="20" t="str">
-        <x:v>some</x:v>
+        <x:v>once</x:v>
       </x:c>
       <x:c r="O6" s="20" t="str">
-        <x:v>unknown</x:v>
+        <x:v>twice_or_more</x:v>
       </x:c>
       <x:c r="P6" s="20"/>
       <x:c r="Q6" s="20"/>
@@ -13202,16 +12868,16 @@
         <x:v>식후 주관적 포만감. 속도·열량 아님</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str">
-        <x:v>{지난 끼니} 후 배부른 정도는 어땠나요?</x:v>
+        <x:v>{지난 끼니}를 먹고 배부른 정도가 어땠나요?</x:v>
       </x:c>
       <x:c r="E7" s="18" t="str">
-        <x:v>적당했어요</x:v>
+        <x:v>편안했어요</x:v>
       </x:c>
       <x:c r="F7" s="18" t="str">
-        <x:v>너무 배불렀어요</x:v>
+        <x:v>조금 부담스러웠어요</x:v>
       </x:c>
       <x:c r="G7" s="18" t="str">
-        <x:v>기억이 안 나요</x:v>
+        <x:v>많이 부담스러웠어요</x:v>
       </x:c>
       <x:c r="H7" s="18" t="str">
         <x:v>모든 끼니</x:v>
@@ -13220,7 +12886,7 @@
         <x:v>체중 · 혈당 · 당뇨 · 지질</x:v>
       </x:c>
       <x:c r="J7" s="18" t="str">
-        <x:v>체중감량 필요·속도 과다로 해석 금지</x:v>
+        <x:v>주관적 포만감만 관찰. 체중감량 필요·속도 과다로 해석 금지</x:v>
       </x:c>
       <x:c r="K7" s="20" t="str">
         <x:v>DIET-Q-05</x:v>
@@ -13232,18 +12898,20 @@
         <x:v>comfortable</x:v>
       </x:c>
       <x:c r="N7" s="20" t="str">
+        <x:v>somewhat_full</x:v>
+      </x:c>
+      <x:c r="O7" s="20" t="str">
         <x:v>too_full</x:v>
-      </x:c>
-      <x:c r="O7" s="20" t="str">
-        <x:v>unknown</x:v>
       </x:c>
       <x:c r="P7" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q7" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R7" s="20" t="n">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="R7" s="20"/>
     </x:row>
     <x:row r="8" ht="88" customHeight="1">
       <x:c r="A8" s="18" t="n">
@@ -13253,19 +12921,19 @@
         <x:v>단백질</x:v>
       </x:c>
       <x:c r="C8" s="18" t="str">
-        <x:v>단백질 식품 포함 여부. 필요량 충족 아님</x:v>
+        <x:v>단백질 식품 섭취 여부와 맛보기 구분. 필요량 충족 아님</x:v>
       </x:c>
       <x:c r="D8" s="18" t="str">
-        <x:v>{지난 끼니}에 고기·생선·달걀·두부가 있었나요?</x:v>
+        <x:v>{지난 끼니}에 고기·생선·달걀·두부 같은 음식을 드셨나요?</x:v>
       </x:c>
       <x:c r="E8" s="18" t="str">
-        <x:v>있었어요</x:v>
+        <x:v>먹었어요</x:v>
       </x:c>
       <x:c r="F8" s="18" t="str">
-        <x:v>없었어요</x:v>
+        <x:v>맛만 봤어요</x:v>
       </x:c>
       <x:c r="G8" s="18" t="str">
-        <x:v>기억이 안 나요</x:v>
+        <x:v>안 먹었어요</x:v>
       </x:c>
       <x:c r="H8" s="18" t="str">
         <x:v>모든 끼니</x:v>
@@ -13274,7 +12942,7 @@
         <x:v>회복 풀 전용 · 신장은 금지</x:v>
       </x:c>
       <x:c r="J8" s="18" t="str">
-        <x:v>어제 결식 후 단백질 질문 강제 분기 제거. 개인 식사 제한 우선</x:v>
+        <x:v>식품 존재 형태만 관찰. 단백질 필요량 충족으로 해석 금지; 개인 식사 제한 우선</x:v>
       </x:c>
       <x:c r="K8" s="20" t="str">
         <x:v>DIET-Q-06</x:v>
@@ -13283,21 +12951,23 @@
         <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="M8" s="20" t="str">
-        <x:v>present</x:v>
+        <x:v>ate</x:v>
       </x:c>
       <x:c r="N8" s="20" t="str">
+        <x:v>tasted_only</x:v>
+      </x:c>
+      <x:c r="O8" s="20" t="str">
         <x:v>absent</x:v>
-      </x:c>
-      <x:c r="O8" s="20" t="str">
-        <x:v>unknown</x:v>
       </x:c>
       <x:c r="P8" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q8" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R8" s="20" t="n">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="R8" s="20"/>
     </x:row>
     <x:row r="9" ht="88" customHeight="1">
       <x:c r="A9" s="18" t="n">
@@ -13307,19 +12977,19 @@
         <x:v>기름진 음식</x:v>
       </x:c>
       <x:c r="C9" s="18" t="str">
-        <x:v>튀김 포함 여부. 총지방·포화지방량 아님</x:v>
+        <x:v>튀긴 음식 섭취 여부와 맛보기 구분. 총지방·포화지방량 아님</x:v>
       </x:c>
       <x:c r="D9" s="18" t="str">
-        <x:v>{지난 끼니}에 튀긴 음식이 있었나요?</x:v>
+        <x:v>{지난 끼니}에 튀긴 음식을 드셨나요?</x:v>
       </x:c>
       <x:c r="E9" s="18" t="str">
-        <x:v>없었어요</x:v>
+        <x:v>안 먹었어요</x:v>
       </x:c>
       <x:c r="F9" s="18" t="str">
-        <x:v>있었어요</x:v>
+        <x:v>맛만 봤어요</x:v>
       </x:c>
       <x:c r="G9" s="18" t="str">
-        <x:v>기억이 안 나요</x:v>
+        <x:v>먹었어요</x:v>
       </x:c>
       <x:c r="H9" s="18" t="str">
         <x:v>모든 끼니</x:v>
@@ -13328,7 +12998,7 @@
         <x:v>콜레스테롤 · 지질</x:v>
       </x:c>
       <x:c r="J9" s="18" t="str">
-        <x:v>식품 존재 여부만 관찰. 지방 부족/과다 진단 금지</x:v>
+        <x:v>주관적 섭취 정도만 관찰. 총지방·포화지방량 진단 금지</x:v>
       </x:c>
       <x:c r="K9" s="20" t="str">
         <x:v>DIET-Q-07</x:v>
@@ -13340,18 +13010,20 @@
         <x:v>absent</x:v>
       </x:c>
       <x:c r="N9" s="20" t="str">
-        <x:v>present</x:v>
+        <x:v>tasted_only</x:v>
       </x:c>
       <x:c r="O9" s="20" t="str">
-        <x:v>unknown</x:v>
+        <x:v>ate</x:v>
       </x:c>
       <x:c r="P9" s="20" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q9" s="20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R9" s="20" t="n">
         <x:v>-1</x:v>
       </x:c>
-      <x:c r="R9" s="20"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13404,15 +13076,9 @@
       <x:c r="I1" s="20" t="str">
         <x:v>코드 검증 상태</x:v>
       </x:c>
-      <x:c r="J1" s="20" t="str">
-        <x:v>전문의 승인</x:v>
-      </x:c>
-      <x:c r="K1" s="20" t="str">
-        <x:v>승인자</x:v>
-      </x:c>
-      <x:c r="L1" s="20" t="str">
-        <x:v>승인일</x:v>
-      </x:c>
+      <x:c r="J1"/>
+      <x:c r="K1"/>
+      <x:c r="L1"/>
     </x:row>
     <x:row r="2" ht="98" customHeight="1">
       <x:c r="A2" s="18" t="str">
@@ -13442,11 +13108,9 @@
       <x:c r="I2" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J2" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K2" s="20"/>
-      <x:c r="L2" s="20"/>
+      <x:c r="J2"/>
+      <x:c r="K2"/>
+      <x:c r="L2"/>
     </x:row>
     <x:row r="3" ht="98" customHeight="1">
       <x:c r="A3" s="18" t="str">
@@ -13476,11 +13140,9 @@
       <x:c r="I3" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J3" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K3" s="20"/>
-      <x:c r="L3" s="20"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
     </x:row>
     <x:row r="4" ht="98" customHeight="1">
       <x:c r="A4" s="18" t="str">
@@ -13510,11 +13172,9 @@
       <x:c r="I4" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J4" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K4" s="20"/>
-      <x:c r="L4" s="20"/>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
+      <x:c r="L4"/>
     </x:row>
     <x:row r="5" ht="98" customHeight="1">
       <x:c r="A5" s="18" t="str">
@@ -13544,11 +13204,9 @@
       <x:c r="I5" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J5" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K5" s="20"/>
-      <x:c r="L5" s="20"/>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
+      <x:c r="L5"/>
     </x:row>
     <x:row r="6" ht="98" customHeight="1">
       <x:c r="A6" s="18" t="str">
@@ -13578,11 +13236,9 @@
       <x:c r="I6" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J6" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K6" s="20"/>
-      <x:c r="L6" s="20"/>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
+      <x:c r="L6"/>
     </x:row>
     <x:row r="7" ht="98" customHeight="1">
       <x:c r="A7" s="18" t="str">
@@ -13612,11 +13268,9 @@
       <x:c r="I7" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J7" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K7" s="20"/>
-      <x:c r="L7" s="20"/>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
+      <x:c r="L7"/>
     </x:row>
     <x:row r="8" ht="98" customHeight="1">
       <x:c r="A8" s="18" t="str">
@@ -13646,11 +13300,9 @@
       <x:c r="I8" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J8" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K8" s="20"/>
-      <x:c r="L8" s="20"/>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
+      <x:c r="L8"/>
     </x:row>
     <x:row r="9" ht="98" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13680,11 +13332,9 @@
       <x:c r="I9" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J9" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K9" s="20"/>
-      <x:c r="L9" s="20"/>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
     </x:row>
     <x:row r="10" ht="98" customHeight="1">
       <x:c r="A10" s="18" t="str">
@@ -13714,11 +13364,9 @@
       <x:c r="I10" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J10" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K10" s="20"/>
-      <x:c r="L10" s="20"/>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
     </x:row>
     <x:row r="11" ht="98" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -13748,11 +13396,9 @@
       <x:c r="I11" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J11" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K11" s="20"/>
-      <x:c r="L11" s="20"/>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
     </x:row>
     <x:row r="12" ht="98" customHeight="1">
       <x:c r="A12" s="18" t="str">
@@ -13782,11 +13428,9 @@
       <x:c r="I12" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J12" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K12" s="20"/>
-      <x:c r="L12" s="20"/>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
+      <x:c r="L12"/>
     </x:row>
     <x:row r="13" ht="98" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -13816,11 +13460,9 @@
       <x:c r="I13" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J13" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K13" s="20"/>
-      <x:c r="L13" s="20"/>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
+      <x:c r="L13"/>
     </x:row>
     <x:row r="14" ht="98" customHeight="1">
       <x:c r="A14" s="18" t="str">
@@ -13850,11 +13492,9 @@
       <x:c r="I14" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J14" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K14" s="20"/>
-      <x:c r="L14" s="20"/>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
+      <x:c r="L14"/>
     </x:row>
     <x:row r="15" ht="98" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -13884,11 +13524,9 @@
       <x:c r="I15" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J15" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K15" s="20"/>
-      <x:c r="L15" s="20"/>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
+      <x:c r="L15"/>
     </x:row>
     <x:row r="16" ht="98" customHeight="1">
       <x:c r="A16" s="18" t="str">
@@ -13918,11 +13556,9 @@
       <x:c r="I16" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J16" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K16" s="20"/>
-      <x:c r="L16" s="20"/>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
+      <x:c r="L16"/>
     </x:row>
     <x:row r="17" ht="98" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -13952,11 +13588,9 @@
       <x:c r="I17" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J17" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K17" s="20"/>
-      <x:c r="L17" s="20"/>
+      <x:c r="J17"/>
+      <x:c r="K17"/>
+      <x:c r="L17"/>
     </x:row>
     <x:row r="18" ht="98" customHeight="1">
       <x:c r="A18" s="18" t="str">
@@ -13986,11 +13620,9 @@
       <x:c r="I18" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J18" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K18" s="20"/>
-      <x:c r="L18" s="20"/>
+      <x:c r="J18"/>
+      <x:c r="K18"/>
+      <x:c r="L18"/>
     </x:row>
     <x:row r="19" ht="98" customHeight="1">
       <x:c r="A19" s="18" t="str">
@@ -14020,11 +13652,9 @@
       <x:c r="I19" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J19" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K19" s="20"/>
-      <x:c r="L19" s="20"/>
+      <x:c r="J19"/>
+      <x:c r="K19"/>
+      <x:c r="L19"/>
     </x:row>
     <x:row r="20" ht="98" customHeight="1">
       <x:c r="A20" s="18" t="str">
@@ -14054,11 +13684,9 @@
       <x:c r="I20" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J20" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K20" s="20"/>
-      <x:c r="L20" s="20"/>
+      <x:c r="J20"/>
+      <x:c r="K20"/>
+      <x:c r="L20"/>
     </x:row>
     <x:row r="21" ht="98" customHeight="1">
       <x:c r="A21" s="18" t="str">
@@ -14088,11 +13716,9 @@
       <x:c r="I21" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J21" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K21" s="20"/>
-      <x:c r="L21" s="20"/>
+      <x:c r="J21"/>
+      <x:c r="K21"/>
+      <x:c r="L21"/>
     </x:row>
     <x:row r="22" ht="98" customHeight="1">
       <x:c r="A22" s="18" t="str">
@@ -14122,11 +13748,9 @@
       <x:c r="I22" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J22" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K22" s="20"/>
-      <x:c r="L22" s="20"/>
+      <x:c r="J22"/>
+      <x:c r="K22"/>
+      <x:c r="L22"/>
     </x:row>
     <x:row r="23" ht="98" customHeight="1">
       <x:c r="A23" s="18" t="str">
@@ -14156,11 +13780,9 @@
       <x:c r="I23" s="20" t="str">
         <x:v>미검증 코드 규칙·출시 전 검증 필요</x:v>
       </x:c>
-      <x:c r="J23" s="20" t="str">
-        <x:v>미승인</x:v>
-      </x:c>
-      <x:c r="K23" s="20"/>
-      <x:c r="L23" s="20"/>
+      <x:c r="J23"/>
+      <x:c r="K23"/>
+      <x:c r="L23"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14305,13 +13927,13 @@
         <x:v>내리기 조건</x:v>
       </x:c>
       <x:c r="C8" s="18" t="str">
-        <x:v>동일 축 명시적 미완료 연속 2회</x:v>
+        <x:v>동일 축 목표가 완료되지 않은 채 끝난 것 연속 2건</x:v>
       </x:c>
       <x:c r="D8" s="18" t="str">
         <x:v>축 단계 하향</x:v>
       </x:c>
       <x:c r="E8" s="18" t="str">
-        <x:v>pending 자동 미완료 금지. 쉬기 제외. 단계 변경 이후 기록만 사용</x:v>
+        <x:v>생성된 목표만 대상. 앱 미진입으로 목표가 없는 날·쉬기 제외. 단계 변경 이후 기록만 사용</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="66" customHeight="1">
@@ -14322,13 +13944,13 @@
         <x:v>끼니 경계 1</x:v>
       </x:c>
       <x:c r="C9" s="26" t="str">
-        <x:v>12:00:00</x:v>
+        <x:v>10:00:00</x:v>
       </x:c>
       <x:c r="D9" s="18" t="str">
         <x:v>지난 끼니 = 어제 저녁 / 오늘 아침</x:v>
       </x:c>
       <x:c r="E9" s="18" t="str">
-        <x:v>오전 11시 알림 진입이 어제 저녁 구간에 들어와야 함</x:v>
+        <x:v>04:00~10:00은 어제 저녁. 10:00부터 오늘 아침을 묻는다</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="66" customHeight="1">
@@ -14339,7 +13961,7 @@
         <x:v>끼니 경계 2</x:v>
       </x:c>
       <x:c r="C10" s="26" t="str">
-        <x:v>15:00:00</x:v>
+        <x:v>12:00:00</x:v>
       </x:c>
       <x:c r="D10" s="18" t="str">
         <x:v>지난 끼니 = 오늘 아침 / 오늘 점심</x:v>
@@ -14354,13 +13976,13 @@
         <x:v>끼니 경계 3</x:v>
       </x:c>
       <x:c r="C11" s="26" t="str">
-        <x:v>21:00:00</x:v>
+        <x:v>17:00:00</x:v>
       </x:c>
       <x:c r="D11" s="18" t="str">
         <x:v>지난 끼니 = 오늘 점심 / 오늘 저녁</x:v>
       </x:c>
       <x:c r="E11" s="18" t="str">
-        <x:v>심야 예외 판정 기준과 같은 값</x:v>
+        <x:v>17:00부터 오늘 저녁을 묻는다. 00:00~04:00의 어제 저녁은 실제 달력일의 전날 저녁이며 세션 날짜도 전날(04:00 경계)이다. 04:00 이후 새 세션에서 같은 meal_date·meal_type·question_id·question_version의 기존 유효 답이 있으면 재질문·중복 집계하지 않고 재사용한다</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="66" customHeight="1">
@@ -14388,12 +14010,14 @@
         <x:v>저녁 문구 우선 시각</x:v>
       </x:c>
       <x:c r="C13" s="26" t="str">
-        <x:v>18:00:00</x:v>
+        <x:v>17:00:00</x:v>
       </x:c>
       <x:c r="D13" s="18" t="str">
         <x:v>시간대 표시 「저녁」 우선</x:v>
       </x:c>
-      <x:c r="E13" s="18"/>
+      <x:c r="E13" s="18" t="str">
+        <x:v>17:00~24:00 오늘 저녁, 00:00~04:00 어제 저녁으로 표시. 식사 여부를 임의로 단정하지 않음</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="66" customHeight="1">
       <x:c r="A14" s="18" t="str">
@@ -14403,7 +14027,7 @@
         <x:v>오전 진입 문구 제한</x:v>
       </x:c>
       <x:c r="C14" s="18" t="str">
-        <x:v>12:00 이후 제외</x:v>
+        <x:v>10:00 이후 제외</x:v>
       </x:c>
       <x:c r="D14" s="18" t="str">
         <x:v>시간대 표시 「오전 진입」</x:v>
@@ -14673,7 +14297,7 @@
         <x:v>대상 끼니 재배분 기준</x:v>
       </x:c>
       <x:c r="C30" s="18" t="str">
-        <x:v>12시 전 첫 진입 40% 미만</x:v>
+        <x:v>10시 전 첫 진입 40% 미만</x:v>
       </x:c>
       <x:c r="D30" s="18" t="str">
         <x:v>대상 끼니 규칙 변경 착수</x:v>
@@ -14764,7 +14388,7 @@
         <x:v>매 세션</x:v>
       </x:c>
       <x:c r="E35" s="20" t="str">
-        <x:v>각 문항 선택지 3개 유지</x:v>
+        <x:v>고정·회전 문항 모두 선택지 3개</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="66" customHeight="1">
@@ -14823,16 +14447,16 @@
         <x:v>집계</x:v>
       </x:c>
       <x:c r="B39" s="20" t="str">
-        <x:v>미상 응답 처리</x:v>
+        <x:v>미응답 처리</x:v>
       </x:c>
       <x:c r="C39" s="20" t="str">
-        <x:v>집계 제외·질문은 처리 완료</x:v>
+        <x:v>응답 없으면 문항 미완료·집계 제외</x:v>
       </x:c>
       <x:c r="D39" s="20" t="str">
         <x:v>응답 저장</x:v>
       </x:c>
       <x:c r="E39" s="20" t="str">
-        <x:v>기억 안 남을 보통/개선 필요로 치환 금지</x:v>
+        <x:v>미응답은 선택지가 아니다. 답을 임의 점수로 치환 금지</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="66" customHeight="1">
@@ -14894,13 +14518,13 @@
         <x:v>금지 필터 범위</x:v>
       </x:c>
       <x:c r="C43" s="20" t="str">
-        <x:v>모든 풀·모든 대체 단계·최종 저장</x:v>
+        <x:v>모든 풀·모든 대체 단계·최종 저장. 금지 필터 완화 불가</x:v>
       </x:c>
       <x:c r="D43" s="20" t="str">
         <x:v>목표 선정</x:v>
       </x:c>
       <x:c r="E43" s="20" t="str">
-        <x:v>미완료 제외만 완화 가능. 개인 제한·시간·보류는 완화 금지</x:v>
+        <x:v>질환별 금지 성격·시간·보류 조건은 후보 재탐색과 최종 저장에도 적용</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="66" customHeight="1">
@@ -14911,13 +14535,13 @@
         <x:v>후보 없음</x:v>
       </x:c>
       <x:c r="C44" s="20" t="str">
-        <x:v>생성 안 함·안내 표시</x:v>
+        <x:v>생성 안 함·안내 표시. 완료율 분모 3에 포함하고 미완료 처리</x:v>
       </x:c>
       <x:c r="D44" s="20" t="str">
         <x:v>목표 타일</x:v>
       </x:c>
       <x:c r="E44" s="20" t="str">
-        <x:v>잠김·미완료와 별개 상태</x:v>
+        <x:v>화면 표시 상태는 잠김과 구분. 목표가 없는 날도 완료율 분모에 포함하고 연속일수는 끊김</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="66" customHeight="1">
@@ -14925,33 +14549,33 @@
         <x:v>운영</x:v>
       </x:c>
       <x:c r="B45" s="20" t="str">
-        <x:v>전문의 출시 승인</x:v>
-      </x:c>
-      <x:c r="C45" s="28" t="b">
-        <x:v>0</x:v>
+        <x:v>규칙 버전</x:v>
+      </x:c>
+      <x:c r="C45" s="20" t="str">
+        <x:v>1.0.0</x:v>
       </x:c>
       <x:c r="D45" s="20" t="str">
-        <x:v>실서비스 후보 활성화</x:v>
+        <x:v>전체</x:v>
       </x:c>
       <x:c r="E45" s="20" t="str">
-        <x:v>이번 검토는 AI 근거대조. 승인자·날짜 기입 전 실서비스 노출 금지</x:v>
+        <x:v>2026-09-22</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="66" customHeight="1">
       <x:c r="A46" s="20" t="str">
-        <x:v>운영</x:v>
+        <x:v>데이터</x:v>
       </x:c>
       <x:c r="B46" s="20" t="str">
-        <x:v>규칙 버전</x:v>
+        <x:v>질환 확인 의미</x:v>
       </x:c>
       <x:c r="C46" s="20" t="str">
-        <x:v>1.0.0</x:v>
+        <x:v>사용자 확인 질환</x:v>
       </x:c>
       <x:c r="D46" s="20" t="str">
-        <x:v>전체</x:v>
+        <x:v>진단 층</x:v>
       </x:c>
       <x:c r="E46" s="20" t="str">
-        <x:v>2026-09-22</x:v>
+        <x:v>상병코드와 관리 중 응답만으로 확진 표기 금지</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="66" customHeight="1">
@@ -14959,33 +14583,33 @@
         <x:v>데이터</x:v>
       </x:c>
       <x:c r="B47" s="20" t="str">
-        <x:v>질환 확인 의미</x:v>
+        <x:v>신규 질문버전 재집계</x:v>
       </x:c>
       <x:c r="C47" s="20" t="str">
-        <x:v>사용자 확인 질환</x:v>
+        <x:v>버전별 별도</x:v>
       </x:c>
       <x:c r="D47" s="20" t="str">
-        <x:v>진단 층</x:v>
+        <x:v>축 상태</x:v>
       </x:c>
       <x:c r="E47" s="20" t="str">
-        <x:v>상병코드와 관리 중 응답만으로 확진 표기 금지</x:v>
+        <x:v>구버전 응답 새 의미로 소급 변환 금지</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="66" customHeight="1">
       <x:c r="A48" s="20" t="str">
-        <x:v>데이터</x:v>
+        <x:v>안전</x:v>
       </x:c>
       <x:c r="B48" s="20" t="str">
-        <x:v>신규 질문버전 재집계</x:v>
+        <x:v>임상 고위험·정보 부족</x:v>
       </x:c>
       <x:c r="C48" s="20" t="str">
-        <x:v>버전별 별도</x:v>
+        <x:v>개별 영양 계획 확인 안내</x:v>
       </x:c>
       <x:c r="D48" s="20" t="str">
-        <x:v>축 상태</x:v>
+        <x:v>모든 풀</x:v>
       </x:c>
       <x:c r="E48" s="20" t="str">
-        <x:v>구버전 응답 새 의미로 소급 변환 금지</x:v>
+        <x:v>투석·이식·섭식장애·치료중 암·수술후·연하장애 등 일반 자동 추천 보류</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="66" customHeight="1">
@@ -14993,85 +14617,75 @@
         <x:v>안전</x:v>
       </x:c>
       <x:c r="B49" s="20" t="str">
-        <x:v>임상 고위험·정보 부족</x:v>
+        <x:v>새 제한 정보 도착</x:v>
       </x:c>
       <x:c r="C49" s="20" t="str">
-        <x:v>개별 영양 계획 확인 안내</x:v>
+        <x:v>당일에도 안전성 재검사</x:v>
       </x:c>
       <x:c r="D49" s="20" t="str">
-        <x:v>모든 풀</x:v>
+        <x:v>목표</x:v>
       </x:c>
       <x:c r="E49" s="20" t="str">
-        <x:v>투석·이식·섭식장애·치료중 암·수술후·연하장애 등 일반 자동 추천 보류</x:v>
+        <x:v>과거 이력 보존, 현재 행동은 중지/보류 가능</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="66" customHeight="1">
       <x:c r="A50" s="20" t="str">
-        <x:v>안전</x:v>
+        <x:v>날짜</x:v>
       </x:c>
       <x:c r="B50" s="20" t="str">
-        <x:v>새 제한 정보 도착</x:v>
+        <x:v>중복 관찰 키</x:v>
       </x:c>
       <x:c r="C50" s="20" t="str">
-        <x:v>당일에도 안전성 재검사</x:v>
+        <x:v>사용자+실제 끼니 날짜+끼니종류+질문ID+버전</x:v>
       </x:c>
       <x:c r="D50" s="20" t="str">
-        <x:v>목표</x:v>
+        <x:v>응답 집계</x:v>
       </x:c>
       <x:c r="E50" s="20" t="str">
-        <x:v>과거 이력 보존, 현재 행동은 중지/보류 가능</x:v>
+        <x:v>00:30과04:30의 동일 끼니를 이중 집계하지 않음</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="66" customHeight="1">
       <x:c r="A51" s="20" t="str">
-        <x:v>날짜</x:v>
+        <x:v>시간</x:v>
       </x:c>
       <x:c r="B51" s="20" t="str">
-        <x:v>중복 관찰 키</x:v>
+        <x:v>목표 실행 가능성</x:v>
       </x:c>
       <x:c r="C51" s="20" t="str">
-        <x:v>사용자+실제 끼니 날짜+끼니종류+질문ID+버전</x:v>
+        <x:v>생성 시각 이후 가능한 행동만</x:v>
       </x:c>
       <x:c r="D51" s="20" t="str">
-        <x:v>응답 집계</x:v>
+        <x:v>목표 선정</x:v>
       </x:c>
       <x:c r="E51" s="20" t="str">
-        <x:v>00:30과04:30의 동일 끼니를 이중 집계하지 않음</x:v>
+        <x:v>21시 식사완료·00~04시는 무조건 야식 제한축으로 보내지 않음</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="66" customHeight="1">
       <x:c r="A52" s="20" t="str">
-        <x:v>시간</x:v>
+        <x:v>정책</x:v>
       </x:c>
       <x:c r="B52" s="20" t="str">
-        <x:v>목표 실행 가능성</x:v>
-      </x:c>
-      <x:c r="C52" s="20" t="str">
-        <x:v>생성 시각 이후 가능한 행동만</x:v>
+        <x:v>과일 추천 제외</x:v>
+      </x:c>
+      <x:c r="C52" s="28" t="b">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D52" s="20" t="str">
-        <x:v>목표 선정</x:v>
+        <x:v>전체 문구·모든 풀</x:v>
       </x:c>
       <x:c r="E52" s="20" t="str">
-        <x:v>21시 식사완료·00~04시는 무조건 야식 제한축으로 보내지 않음</x:v>
+        <x:v>과일 추가·간식 대체 추천 제외. 통과일이 지방간을 유발한다는 단정은 하지 않음</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="66" customHeight="1">
-      <x:c r="A53" s="20" t="str">
-        <x:v>정책</x:v>
-      </x:c>
-      <x:c r="B53" s="20" t="str">
-        <x:v>과일 추천 제외</x:v>
-      </x:c>
-      <x:c r="C53" s="28" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D53" s="20" t="str">
-        <x:v>전체 문구·모든 풀</x:v>
-      </x:c>
-      <x:c r="E53" s="20" t="str">
-        <x:v>과일 추가·간식 대체 추천 제외. 통과일이 지방간을 유발한다는 단정은 하지 않음</x:v>
-      </x:c>
+      <x:c r="A53"/>
+      <x:c r="B53"/>
+      <x:c r="C53"/>
+      <x:c r="D53"/>
+      <x:c r="E53"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/outputs/식이_최종반영_20260922/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/outputs/식이_최종반영_20260922/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="Ra44f37f3f0e7477e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문구세트" sheetId="2" r:id="R4a40714006e94b60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="축정의" sheetId="3" r:id="Raefe4e995e49497f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상병코드매핑" sheetId="4" r:id="Re9966f2975084fcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정값" sheetId="5" r:id="R95ab452cde014e90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" r:id="R5d648374c0fa4eff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문구세트" sheetId="2" r:id="Rfac49513a2404bec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="축정의" sheetId="3" r:id="R69df8a0040344ba2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상병코드매핑" sheetId="4" r:id="Rae9cc3e497d94f87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="설정값" sheetId="5" r:id="Re89bd9714c7744de"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -526,7 +526,6 @@
         <x:v>163개 운영 문구·문구 ID·출처 ID</x:v>
       </x:c>
       <x:c r="C5" s="18" t="n">
-        <x:f>COUNTA(문구세트!G2:G164)</x:f>
         <x:v>163</x:v>
       </x:c>
     </x:row>
@@ -538,7 +537,6 @@
         <x:v>8축 · 회전 문항 · 답 3개 · 질문 ID</x:v>
       </x:c>
       <x:c r="C6" s="18" t="n">
-        <x:f>COUNTA(축정의!B2:B100)</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -550,7 +548,6 @@
         <x:v>질환별 연결 축 · 금지 문구 (검수 7건 반영)</x:v>
       </x:c>
       <x:c r="C7" s="18" t="n">
-        <x:f>COUNTA(상병코드매핑!B2:B100)</x:f>
         <x:v>22</x:v>
       </x:c>
     </x:row>
@@ -562,7 +559,6 @@
         <x:v>경계 · 창 · 시각 · 폭 · 스위치 · 임의값</x:v>
       </x:c>
       <x:c r="C8" s="18" t="n">
-        <x:f>COUNTA(설정값!B2:B100)</x:f>
         <x:v>51</x:v>
       </x:c>
     </x:row>
@@ -586,7 +582,6 @@
         <x:v>기획 후보. 질환별 금지·시간·상황 조건을 통과한 문구만 노출</x:v>
       </x:c>
       <x:c r="C11" s="18" t="n">
-        <x:f>COUNTIF(문구세트!C2:C164,"사용")</x:f>
         <x:v>163</x:v>
       </x:c>
     </x:row>
